--- a/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/site_predictions.xlsx
+++ b/results/02_taxa_assemblage/LDA_Method/ModelFinalized/tables/site_predictions.xlsx
@@ -467,19 +467,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C2" t="b">
         <v>0</v>
       </c>
       <c r="D2" t="n">
-        <v>0.3979544130615865</v>
+        <v>0.3037296531326737</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3950553884478141</v>
+        <v>0.6903124552708763</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2069901984905994</v>
+        <v>0.00595789159645008</v>
       </c>
     </row>
     <row r="3">
@@ -495,13 +495,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.5949985296328048</v>
+        <v>0.7549779646997046</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1909785406588097</v>
+        <v>0.2232141722807523</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2140229297083855</v>
+        <v>0.02180786301954313</v>
       </c>
     </row>
     <row r="4">
@@ -517,13 +517,13 @@
         <v>0</v>
       </c>
       <c r="D4" t="n">
-        <v>0.7657099493399573</v>
+        <v>0.9492885959056093</v>
       </c>
       <c r="E4" t="n">
-        <v>0.05137072820128396</v>
+        <v>0.009458092311179221</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1829193224587587</v>
+        <v>0.04125331178321155</v>
       </c>
     </row>
     <row r="5">
@@ -533,19 +533,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C5" t="b">
         <v>0</v>
       </c>
       <c r="D5" t="n">
-        <v>0.2606663584913853</v>
+        <v>0.6827422689193541</v>
       </c>
       <c r="E5" t="n">
-        <v>0.211922987301288</v>
+        <v>0.3099043346140529</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5274106542073267</v>
+        <v>0.007353396466593118</v>
       </c>
     </row>
     <row r="6">
@@ -561,13 +561,13 @@
         <v>0</v>
       </c>
       <c r="D6" t="n">
-        <v>0.5094992509970396</v>
+        <v>0.7291981555879643</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2315821464456183</v>
+        <v>0.2324373089758153</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2589186025573421</v>
+        <v>0.03836453543622019</v>
       </c>
     </row>
     <row r="7">
@@ -583,13 +583,13 @@
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>0.6312875178917535</v>
+        <v>0.8900437284404139</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1340682833075116</v>
+        <v>0.08199228454250239</v>
       </c>
       <c r="F7" t="n">
-        <v>0.2346441988007349</v>
+        <v>0.02796398701708373</v>
       </c>
     </row>
     <row r="8">
@@ -599,19 +599,19 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8" t="b">
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2651633191622352</v>
+        <v>0.6618228397491238</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1982638606600048</v>
+        <v>0.00525600905422868</v>
       </c>
       <c r="F8" t="n">
-        <v>0.53657282017776</v>
+        <v>0.3329211511966476</v>
       </c>
     </row>
     <row r="9">
@@ -621,19 +621,19 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C9" t="b">
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.1432129695094798</v>
+        <v>0.6171500216578977</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3579381814661244</v>
+        <v>0.01727928817999209</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4988488490243957</v>
+        <v>0.3655706901621102</v>
       </c>
     </row>
     <row r="10">
@@ -643,19 +643,19 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C10" t="b">
         <v>0</v>
       </c>
       <c r="D10" t="n">
-        <v>0.3143515803763665</v>
+        <v>0.5160208336064882</v>
       </c>
       <c r="E10" t="n">
-        <v>0.107901244914448</v>
+        <v>0.0005253840749611437</v>
       </c>
       <c r="F10" t="n">
-        <v>0.5777471747091855</v>
+        <v>0.4834537823185508</v>
       </c>
     </row>
     <row r="11">
@@ -665,19 +665,19 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C11" t="b">
         <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>0.3391667640067607</v>
+        <v>0.6745690641552827</v>
       </c>
       <c r="E11" t="n">
-        <v>0.05725161249704237</v>
+        <v>0.0003462145174378372</v>
       </c>
       <c r="F11" t="n">
-        <v>0.603581623496197</v>
+        <v>0.3250847213272795</v>
       </c>
     </row>
     <row r="12">
@@ -687,19 +687,19 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C12" t="b">
         <v>0</v>
       </c>
       <c r="D12" t="n">
-        <v>0.06605911063609145</v>
+        <v>0.5303219604409952</v>
       </c>
       <c r="E12" t="n">
-        <v>0.5933050773125889</v>
+        <v>0.09586851396670071</v>
       </c>
       <c r="F12" t="n">
-        <v>0.3406358120513198</v>
+        <v>0.3738095255923041</v>
       </c>
     </row>
     <row r="13">
@@ -709,19 +709,19 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C13" t="b">
         <v>0</v>
       </c>
       <c r="D13" t="n">
-        <v>0.1151649745548738</v>
+        <v>0.5829158822676745</v>
       </c>
       <c r="E13" t="n">
-        <v>0.4890404597841356</v>
+        <v>0.04962488230654533</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3957945656609906</v>
+        <v>0.3674592354257801</v>
       </c>
     </row>
     <row r="14">
@@ -737,13 +737,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.6583739330518341</v>
+        <v>0.8925015443865257</v>
       </c>
       <c r="E14" t="n">
-        <v>0.04903362239947497</v>
+        <v>0.001392888448577244</v>
       </c>
       <c r="F14" t="n">
-        <v>0.2925924445486909</v>
+        <v>0.1061055671648971</v>
       </c>
     </row>
     <row r="15">
@@ -753,19 +753,19 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C15" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2892190106188982</v>
+        <v>0.6797853389573452</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1261443292394772</v>
+        <v>0.001605521941767586</v>
       </c>
       <c r="F15" t="n">
-        <v>0.5846366601416245</v>
+        <v>0.3186091391008874</v>
       </c>
     </row>
     <row r="16">
@@ -781,13 +781,13 @@
         <v>0</v>
       </c>
       <c r="D16" t="n">
-        <v>0.02189130654821599</v>
+        <v>0.0615697138041057</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8366690913278629</v>
+        <v>0.9315717769394901</v>
       </c>
       <c r="F16" t="n">
-        <v>0.141439602123921</v>
+        <v>0.006858509256404225</v>
       </c>
     </row>
     <row r="17">
@@ -797,19 +797,19 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C17" t="b">
         <v>0</v>
       </c>
       <c r="D17" t="n">
-        <v>0.3934065782265438</v>
+        <v>0.8760724866588054</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08567588817597829</v>
+        <v>0.002774140788666093</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5209175335974778</v>
+        <v>0.1211533725525286</v>
       </c>
     </row>
     <row r="18">
@@ -825,13 +825,13 @@
         <v>0</v>
       </c>
       <c r="D18" t="n">
-        <v>0.01057209299045773</v>
+        <v>0.01801144545017428</v>
       </c>
       <c r="E18" t="n">
-        <v>0.9387781482159063</v>
+        <v>0.977570054532192</v>
       </c>
       <c r="F18" t="n">
-        <v>0.05064975879363601</v>
+        <v>0.004418500017633537</v>
       </c>
     </row>
     <row r="19">
@@ -847,13 +847,13 @@
         <v>0</v>
       </c>
       <c r="D19" t="n">
-        <v>0.05015030052292511</v>
+        <v>0.3011947752800081</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7606367527226991</v>
+        <v>0.6530167736053418</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1892129467543756</v>
+        <v>0.04578845111465003</v>
       </c>
     </row>
     <row r="20">
@@ -869,13 +869,13 @@
         <v>0</v>
       </c>
       <c r="D20" t="n">
-        <v>0.7074840396725948</v>
+        <v>0.9109499714381588</v>
       </c>
       <c r="E20" t="n">
-        <v>0.02800025325076136</v>
+        <v>0.000469285088487569</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2645157070766438</v>
+        <v>0.08858074347335368</v>
       </c>
     </row>
     <row r="21">
@@ -885,19 +885,19 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C21" t="b">
         <v>0</v>
       </c>
       <c r="D21" t="n">
-        <v>0.05527809142119942</v>
+        <v>0.7987295111591375</v>
       </c>
       <c r="E21" t="n">
-        <v>0.2178188806532443</v>
+        <v>0.0673264366529395</v>
       </c>
       <c r="F21" t="n">
-        <v>0.7269030279255563</v>
+        <v>0.133944052187923</v>
       </c>
     </row>
     <row r="22">
@@ -913,13 +913,13 @@
         <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>0.6138112245324661</v>
+        <v>0.9424348866664027</v>
       </c>
       <c r="E22" t="n">
-        <v>0.009081439841221317</v>
+        <v>5.575989891927121e-05</v>
       </c>
       <c r="F22" t="n">
-        <v>0.3771073356263126</v>
+        <v>0.057509353434678</v>
       </c>
     </row>
     <row r="23">
@@ -935,13 +935,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>0.08679686443439495</v>
+        <v>0.3112830612792064</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6793072036662459</v>
+        <v>0.6510800661099009</v>
       </c>
       <c r="F23" t="n">
-        <v>0.2338959318993592</v>
+        <v>0.03763687261089275</v>
       </c>
     </row>
     <row r="24">
@@ -957,13 +957,13 @@
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2600884019156972</v>
+        <v>0.06781004593069323</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5800151914381889</v>
+        <v>0.9318330860001098</v>
       </c>
       <c r="F24" t="n">
-        <v>0.1598964066461138</v>
+        <v>0.0003568680691969574</v>
       </c>
     </row>
     <row r="25">
@@ -979,13 +979,13 @@
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1456320981065432</v>
+        <v>0.04738077615763178</v>
       </c>
       <c r="E25" t="n">
-        <v>0.7081546184779228</v>
+        <v>0.9516552204819284</v>
       </c>
       <c r="F25" t="n">
-        <v>0.1462132834155342</v>
+        <v>0.0009640033604398352</v>
       </c>
     </row>
     <row r="26">
@@ -1001,13 +1001,13 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>0.02582836432180469</v>
+        <v>0.01109114251178627</v>
       </c>
       <c r="E26" t="n">
-        <v>0.8931347399965482</v>
+        <v>0.9883305097487155</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08103689568164713</v>
+        <v>0.0005783477394981822</v>
       </c>
     </row>
     <row r="27">
@@ -1023,13 +1023,13 @@
         <v>0</v>
       </c>
       <c r="D27" t="n">
-        <v>0.04080816530687143</v>
+        <v>0.0001204707745810667</v>
       </c>
       <c r="E27" t="n">
-        <v>0.7780145750585808</v>
+        <v>0.9998794689201407</v>
       </c>
       <c r="F27" t="n">
-        <v>0.1811772596345478</v>
+        <v>6.030527829743758e-08</v>
       </c>
     </row>
     <row r="28">
@@ -1039,19 +1039,19 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C28" t="b">
         <v>1</v>
       </c>
       <c r="D28" t="n">
-        <v>0.1596257613623493</v>
+        <v>0.6319244694963377</v>
       </c>
       <c r="E28" t="n">
-        <v>0.5521649088718755</v>
+        <v>0.3018787627593236</v>
       </c>
       <c r="F28" t="n">
-        <v>0.2882093297657751</v>
+        <v>0.06619676774433855</v>
       </c>
     </row>
     <row r="29">
@@ -1061,19 +1061,19 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C29" t="b">
         <v>0</v>
       </c>
       <c r="D29" t="n">
-        <v>0.001229127770905054</v>
+        <v>0.0004855123831322282</v>
       </c>
       <c r="E29" t="n">
-        <v>0.02132133669611543</v>
+        <v>0.9995144657488628</v>
       </c>
       <c r="F29" t="n">
-        <v>0.9774495355329795</v>
+        <v>2.186800487329754e-08</v>
       </c>
     </row>
     <row r="30">
@@ -1089,13 +1089,13 @@
         <v>1</v>
       </c>
       <c r="D30" t="n">
-        <v>0.005816411337875054</v>
+        <v>0.0008544455980962394</v>
       </c>
       <c r="E30" t="n">
-        <v>0.9265482100880885</v>
+        <v>0.9991093822268066</v>
       </c>
       <c r="F30" t="n">
-        <v>0.06763537857403647</v>
+        <v>3.617217509737698e-05</v>
       </c>
     </row>
     <row r="31">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D31" t="n">
-        <v>0.08329284479424967</v>
+        <v>0.4542301096407368</v>
       </c>
       <c r="E31" t="n">
-        <v>0.6310771163816598</v>
+        <v>0.4979908041829406</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2856300388240906</v>
+        <v>0.04777908617632246</v>
       </c>
     </row>
     <row r="32">
@@ -1133,13 +1133,13 @@
         <v>0</v>
       </c>
       <c r="D32" t="n">
-        <v>0.009439817446752125</v>
+        <v>0.04100645633944333</v>
       </c>
       <c r="E32" t="n">
-        <v>0.8170671487792367</v>
+        <v>0.9534373139204806</v>
       </c>
       <c r="F32" t="n">
-        <v>0.1734930337740112</v>
+        <v>0.005556229740076106</v>
       </c>
     </row>
     <row r="33">
@@ -1149,19 +1149,19 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C33" t="b">
         <v>0</v>
       </c>
       <c r="D33" t="n">
-        <v>0.01381450715060746</v>
+        <v>0.9762601302013029</v>
       </c>
       <c r="E33" t="n">
-        <v>0.000770323871655327</v>
+        <v>0.0235927948594262</v>
       </c>
       <c r="F33" t="n">
-        <v>0.9854151689777372</v>
+        <v>0.0001470749392710463</v>
       </c>
     </row>
     <row r="34">
@@ -1177,13 +1177,13 @@
         <v>0</v>
       </c>
       <c r="D34" t="n">
-        <v>0.02058516851109113</v>
+        <v>0.05120782384310623</v>
       </c>
       <c r="E34" t="n">
-        <v>0.6623154055431466</v>
+        <v>0.947294566763937</v>
       </c>
       <c r="F34" t="n">
-        <v>0.3170994259457623</v>
+        <v>0.001497609392956736</v>
       </c>
     </row>
     <row r="35">
@@ -1199,13 +1199,13 @@
         <v>0</v>
       </c>
       <c r="D35" t="n">
-        <v>0.7780617690585538</v>
+        <v>0.9782162929890216</v>
       </c>
       <c r="E35" t="n">
-        <v>0.02436450457396528</v>
+        <v>0.004513643491007896</v>
       </c>
       <c r="F35" t="n">
-        <v>0.1975737263674808</v>
+        <v>0.01727006351997054</v>
       </c>
     </row>
     <row r="36">
@@ -1221,13 +1221,13 @@
         <v>0</v>
       </c>
       <c r="D36" t="n">
-        <v>0.5447249073856979</v>
+        <v>0.9940459170713057</v>
       </c>
       <c r="E36" t="n">
-        <v>0.008043320906354739</v>
+        <v>0.002757679561953709</v>
       </c>
       <c r="F36" t="n">
-        <v>0.4472317717079474</v>
+        <v>0.003196403366740476</v>
       </c>
     </row>
     <row r="37">
@@ -1243,13 +1243,13 @@
         <v>0</v>
       </c>
       <c r="D37" t="n">
-        <v>0.118919064957031</v>
+        <v>0.03750834797843938</v>
       </c>
       <c r="E37" t="n">
-        <v>0.7704920686985099</v>
+        <v>0.9618487286206896</v>
       </c>
       <c r="F37" t="n">
-        <v>0.1105888663444591</v>
+        <v>0.0006429234008710849</v>
       </c>
     </row>
     <row r="38">
@@ -1265,13 +1265,13 @@
         <v>0</v>
       </c>
       <c r="D38" t="n">
-        <v>0.05921098612652052</v>
+        <v>0.05799379205924036</v>
       </c>
       <c r="E38" t="n">
-        <v>0.8438763449401256</v>
+        <v>0.9375141028762309</v>
       </c>
       <c r="F38" t="n">
-        <v>0.09691266893335392</v>
+        <v>0.004492105064528688</v>
       </c>
     </row>
     <row r="39">
@@ -1287,13 +1287,13 @@
         <v>0</v>
       </c>
       <c r="D39" t="n">
-        <v>0.04985797943100374</v>
+        <v>0.0009102696195508353</v>
       </c>
       <c r="E39" t="n">
-        <v>0.7255130691871707</v>
+        <v>0.9990886696100363</v>
       </c>
       <c r="F39" t="n">
-        <v>0.2246289513818256</v>
+        <v>1.060770413015859e-06</v>
       </c>
     </row>
     <row r="40">
@@ -1303,19 +1303,19 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C40" t="b">
         <v>0</v>
       </c>
       <c r="D40" t="n">
-        <v>0.06553524113577743</v>
+        <v>0.18080375264479</v>
       </c>
       <c r="E40" t="n">
-        <v>0.05766162054086658</v>
+        <v>0.8190179559512446</v>
       </c>
       <c r="F40" t="n">
-        <v>0.876803138323356</v>
+        <v>0.0001782914039654387</v>
       </c>
     </row>
     <row r="41">
@@ -1331,13 +1331,13 @@
         <v>0</v>
       </c>
       <c r="D41" t="n">
-        <v>0.520145798481491</v>
+        <v>0.9399136649195037</v>
       </c>
       <c r="E41" t="n">
-        <v>0.1411001704728742</v>
+        <v>0.03823086308461114</v>
       </c>
       <c r="F41" t="n">
-        <v>0.3387540310456348</v>
+        <v>0.02185547199588531</v>
       </c>
     </row>
     <row r="42">
@@ -1353,13 +1353,13 @@
         <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>0.03253134359533688</v>
+        <v>0.006032657927697746</v>
       </c>
       <c r="E42" t="n">
-        <v>0.9120136156155023</v>
+        <v>0.9936641065043795</v>
       </c>
       <c r="F42" t="n">
-        <v>0.05545504078916099</v>
+        <v>0.0003032355679228648</v>
       </c>
     </row>
     <row r="43">
@@ -1375,13 +1375,13 @@
         <v>0</v>
       </c>
       <c r="D43" t="n">
-        <v>0.07007357828451086</v>
+        <v>0.03926939857493815</v>
       </c>
       <c r="E43" t="n">
-        <v>0.7954458150958407</v>
+        <v>0.9593802471843942</v>
       </c>
       <c r="F43" t="n">
-        <v>0.1344806066196484</v>
+        <v>0.001350354240667566</v>
       </c>
     </row>
     <row r="44">
@@ -1397,13 +1397,13 @@
         <v>1</v>
       </c>
       <c r="D44" t="n">
-        <v>0.2348456553784846</v>
+        <v>0.4298764090743222</v>
       </c>
       <c r="E44" t="n">
-        <v>0.5403635794827704</v>
+        <v>0.5478353168816952</v>
       </c>
       <c r="F44" t="n">
-        <v>0.224790765138745</v>
+        <v>0.02228827404398263</v>
       </c>
     </row>
     <row r="45">
@@ -1419,13 +1419,13 @@
         <v>0</v>
       </c>
       <c r="D45" t="n">
-        <v>0.7392105983972287</v>
+        <v>0.9876102611056859</v>
       </c>
       <c r="E45" t="n">
-        <v>0.007241235098789395</v>
+        <v>0.0003911048583129162</v>
       </c>
       <c r="F45" t="n">
-        <v>0.253548166503982</v>
+        <v>0.01199863403600105</v>
       </c>
     </row>
     <row r="46">
@@ -1441,13 +1441,13 @@
         <v>1</v>
       </c>
       <c r="D46" t="n">
-        <v>0.1649756126503208</v>
+        <v>0.08739805159057354</v>
       </c>
       <c r="E46" t="n">
-        <v>0.6918238016796342</v>
+        <v>0.9094452642255231</v>
       </c>
       <c r="F46" t="n">
-        <v>0.143200585670045</v>
+        <v>0.003156684183903366</v>
       </c>
     </row>
     <row r="47">
@@ -1457,19 +1457,19 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C47" t="b">
         <v>1</v>
       </c>
       <c r="D47" t="n">
-        <v>0.09360471185791687</v>
+        <v>0.947886244233525</v>
       </c>
       <c r="E47" t="n">
-        <v>0.01499111939960431</v>
+        <v>0.001842106119627295</v>
       </c>
       <c r="F47" t="n">
-        <v>0.8914041687424789</v>
+        <v>0.0502716496468477</v>
       </c>
     </row>
     <row r="48">
@@ -1479,19 +1479,19 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C48" t="b">
         <v>0</v>
       </c>
       <c r="D48" t="n">
-        <v>0.3049790469100993</v>
+        <v>0.689467298100773</v>
       </c>
       <c r="E48" t="n">
-        <v>0.0758135565685318</v>
+        <v>0.0007794014215486559</v>
       </c>
       <c r="F48" t="n">
-        <v>0.619207396521369</v>
+        <v>0.3097533004776784</v>
       </c>
     </row>
     <row r="49">
@@ -1501,19 +1501,19 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C49" t="b">
         <v>1</v>
       </c>
       <c r="D49" t="n">
-        <v>0.1828878323419488</v>
+        <v>0.7378762650907017</v>
       </c>
       <c r="E49" t="n">
-        <v>0.05431701297961558</v>
+        <v>0.001030639319635279</v>
       </c>
       <c r="F49" t="n">
-        <v>0.7627951546784355</v>
+        <v>0.2610930955896629</v>
       </c>
     </row>
     <row r="50">
@@ -1523,19 +1523,19 @@
         </is>
       </c>
       <c r="B50" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C50" t="b">
         <v>0</v>
       </c>
       <c r="D50" t="n">
-        <v>0.2716164295376225</v>
+        <v>0.9634210718624475</v>
       </c>
       <c r="E50" t="n">
-        <v>0.01091231243450609</v>
+        <v>0.0003269426164831581</v>
       </c>
       <c r="F50" t="n">
-        <v>0.7174712580278714</v>
+        <v>0.03625198552106939</v>
       </c>
     </row>
     <row r="51">
@@ -1545,19 +1545,19 @@
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C51" t="b">
         <v>1</v>
       </c>
       <c r="D51" t="n">
-        <v>0.1184751581211329</v>
+        <v>0.6955954911963294</v>
       </c>
       <c r="E51" t="n">
-        <v>0.4218655757863208</v>
+        <v>0.09279590434832725</v>
       </c>
       <c r="F51" t="n">
-        <v>0.4596592660925463</v>
+        <v>0.2116086044553434</v>
       </c>
     </row>
     <row r="52">
@@ -1567,19 +1567,19 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C52" t="b">
         <v>0</v>
       </c>
       <c r="D52" t="n">
-        <v>0.141256675978985</v>
+        <v>0.9347515128870081</v>
       </c>
       <c r="E52" t="n">
-        <v>0.01260133389796639</v>
+        <v>0.0005504364105471069</v>
       </c>
       <c r="F52" t="n">
-        <v>0.8461419901230486</v>
+        <v>0.06469805070244497</v>
       </c>
     </row>
     <row r="53">
@@ -1589,19 +1589,19 @@
         </is>
       </c>
       <c r="B53" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C53" t="b">
         <v>0</v>
       </c>
       <c r="D53" t="n">
-        <v>0.2650179525412105</v>
+        <v>0.9608670484198781</v>
       </c>
       <c r="E53" t="n">
-        <v>0.008958393843342117</v>
+        <v>0.0002179873282394116</v>
       </c>
       <c r="F53" t="n">
-        <v>0.7260236536154474</v>
+        <v>0.03891496425188253</v>
       </c>
     </row>
     <row r="54">
@@ -1617,13 +1617,13 @@
         <v>1</v>
       </c>
       <c r="D54" t="n">
-        <v>0.007065714019164181</v>
+        <v>0.0178426796584742</v>
       </c>
       <c r="E54" t="n">
-        <v>0.9337577938568783</v>
+        <v>0.9711104335134431</v>
       </c>
       <c r="F54" t="n">
-        <v>0.05917649212395739</v>
+        <v>0.01104688682808266</v>
       </c>
     </row>
     <row r="55">
@@ -1633,19 +1633,19 @@
         </is>
       </c>
       <c r="B55" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C55" t="b">
         <v>0</v>
       </c>
       <c r="D55" t="n">
-        <v>0.2708277193305456</v>
+        <v>0.7208970886305259</v>
       </c>
       <c r="E55" t="n">
-        <v>0.08425452182114054</v>
+        <v>0.001771063259898875</v>
       </c>
       <c r="F55" t="n">
-        <v>0.6449177588483139</v>
+        <v>0.2773318481095751</v>
       </c>
     </row>
     <row r="56">
@@ -1661,13 +1661,13 @@
         <v>1</v>
       </c>
       <c r="D56" t="n">
-        <v>0.04886053823860375</v>
+        <v>0.2960441838771857</v>
       </c>
       <c r="E56" t="n">
-        <v>0.7572271719793739</v>
+        <v>0.5647433699175413</v>
       </c>
       <c r="F56" t="n">
-        <v>0.1939122897820223</v>
+        <v>0.1392124462052729</v>
       </c>
     </row>
     <row r="57">
@@ -1677,19 +1677,19 @@
         </is>
       </c>
       <c r="B57" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C57" t="b">
         <v>0</v>
       </c>
       <c r="D57" t="n">
-        <v>0.1127840772787225</v>
+        <v>0.9578617248186783</v>
       </c>
       <c r="E57" t="n">
-        <v>0.01930366280297437</v>
+        <v>0.003776109697250176</v>
       </c>
       <c r="F57" t="n">
-        <v>0.8679122599183032</v>
+        <v>0.03836216548407165</v>
       </c>
     </row>
     <row r="58">
@@ -1699,19 +1699,19 @@
         </is>
       </c>
       <c r="B58" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C58" t="b">
         <v>0</v>
       </c>
       <c r="D58" t="n">
-        <v>0.1248821380380076</v>
+        <v>0.7525505056142198</v>
       </c>
       <c r="E58" t="n">
-        <v>0.3135875619501388</v>
+        <v>0.06009846663408751</v>
       </c>
       <c r="F58" t="n">
-        <v>0.5615303000118536</v>
+        <v>0.1873510277516927</v>
       </c>
     </row>
     <row r="59">
@@ -1721,19 +1721,19 @@
         </is>
       </c>
       <c r="B59" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C59" t="b">
         <v>0</v>
       </c>
       <c r="D59" t="n">
-        <v>0.05597558304211243</v>
+        <v>0.9629070904812574</v>
       </c>
       <c r="E59" t="n">
-        <v>0.01702273553660828</v>
+        <v>0.006771223523192436</v>
       </c>
       <c r="F59" t="n">
-        <v>0.9270016814212793</v>
+        <v>0.03032168599555018</v>
       </c>
     </row>
     <row r="60">
@@ -1743,19 +1743,19 @@
         </is>
       </c>
       <c r="B60" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C60" t="b">
         <v>0</v>
       </c>
       <c r="D60" t="n">
-        <v>0.09030847255708922</v>
+        <v>0.7762488059419119</v>
       </c>
       <c r="E60" t="n">
-        <v>0.270501371040427</v>
+        <v>0.1621623924415754</v>
       </c>
       <c r="F60" t="n">
-        <v>0.6391901564024838</v>
+        <v>0.06158880161651264</v>
       </c>
     </row>
     <row r="61">
@@ -1765,19 +1765,19 @@
         </is>
       </c>
       <c r="B61" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C61" t="b">
         <v>0</v>
       </c>
       <c r="D61" t="n">
-        <v>0.2856059284502256</v>
+        <v>0.707781334526236</v>
       </c>
       <c r="E61" t="n">
-        <v>0.07562389000106905</v>
+        <v>0.001186229028693769</v>
       </c>
       <c r="F61" t="n">
-        <v>0.6387701815487054</v>
+        <v>0.2910324364450703</v>
       </c>
     </row>
     <row r="62">
@@ -1787,19 +1787,19 @@
         </is>
       </c>
       <c r="B62" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C62" t="b">
         <v>0</v>
       </c>
       <c r="D62" t="n">
-        <v>0.2009452685761162</v>
+        <v>0.981571715183071</v>
       </c>
       <c r="E62" t="n">
-        <v>0.003213603583243372</v>
+        <v>7.263973927927669e-05</v>
       </c>
       <c r="F62" t="n">
-        <v>0.7958411278406404</v>
+        <v>0.01835564507764988</v>
       </c>
     </row>
     <row r="63">
@@ -1815,13 +1815,13 @@
         <v>0</v>
       </c>
       <c r="D63" t="n">
-        <v>0.6295615821684791</v>
+        <v>0.9142164576697016</v>
       </c>
       <c r="E63" t="n">
-        <v>0.00867088041666635</v>
+        <v>3.146096330494579e-05</v>
       </c>
       <c r="F63" t="n">
-        <v>0.3617675374148546</v>
+        <v>0.08575208136699347</v>
       </c>
     </row>
     <row r="64">
@@ -1831,19 +1831,19 @@
         </is>
       </c>
       <c r="B64" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C64" t="b">
         <v>0</v>
       </c>
       <c r="D64" t="n">
-        <v>0.3302880254862673</v>
+        <v>0.9109237367199889</v>
       </c>
       <c r="E64" t="n">
-        <v>0.02969666840650232</v>
+        <v>0.08575779462561992</v>
       </c>
       <c r="F64" t="n">
-        <v>0.6400153061072302</v>
+        <v>0.003318468654391134</v>
       </c>
     </row>
     <row r="65">
@@ -1859,13 +1859,13 @@
         <v>0</v>
       </c>
       <c r="D65" t="n">
-        <v>0.6301655853764524</v>
+        <v>0.9963192064309623</v>
       </c>
       <c r="E65" t="n">
-        <v>0.005020879168577798</v>
+        <v>0.00217156139333636</v>
       </c>
       <c r="F65" t="n">
-        <v>0.3648135354549697</v>
+        <v>0.00150923217570136</v>
       </c>
     </row>
     <row r="66">
@@ -1881,13 +1881,13 @@
         <v>0</v>
       </c>
       <c r="D66" t="n">
-        <v>0.1136581035123786</v>
+        <v>0.02365475302861578</v>
       </c>
       <c r="E66" t="n">
-        <v>0.7449776917412592</v>
+        <v>0.9759884914455945</v>
       </c>
       <c r="F66" t="n">
-        <v>0.1413642047463621</v>
+        <v>0.0003567555257897227</v>
       </c>
     </row>
     <row r="67">
@@ -1903,13 +1903,13 @@
         <v>0</v>
       </c>
       <c r="D67" t="n">
-        <v>0.7059346203861132</v>
+        <v>0.9927373357059168</v>
       </c>
       <c r="E67" t="n">
-        <v>0.009542642201750984</v>
+        <v>0.002484653862279218</v>
       </c>
       <c r="F67" t="n">
-        <v>0.2845227374121358</v>
+        <v>0.004778010431803919</v>
       </c>
     </row>
     <row r="68">
@@ -1925,13 +1925,13 @@
         <v>0</v>
       </c>
       <c r="D68" t="n">
-        <v>0.7663001697588284</v>
+        <v>0.9854975996811133</v>
       </c>
       <c r="E68" t="n">
-        <v>0.01923367770519054</v>
+        <v>0.007982235592245744</v>
       </c>
       <c r="F68" t="n">
-        <v>0.214466152535981</v>
+        <v>0.006520164726640864</v>
       </c>
     </row>
     <row r="69">
@@ -1947,13 +1947,13 @@
         <v>0</v>
       </c>
       <c r="D69" t="n">
-        <v>0.7609104711080451</v>
+        <v>0.9840141072092572</v>
       </c>
       <c r="E69" t="n">
-        <v>0.02081614227981868</v>
+        <v>0.009323926562663903</v>
       </c>
       <c r="F69" t="n">
-        <v>0.2182733866121362</v>
+        <v>0.006661966228078984</v>
       </c>
     </row>
     <row r="70">
@@ -1969,13 +1969,13 @@
         <v>0</v>
       </c>
       <c r="D70" t="n">
-        <v>0.03733685701188988</v>
+        <v>0.003495271975938557</v>
       </c>
       <c r="E70" t="n">
-        <v>0.553871693779349</v>
+        <v>0.9964916829454301</v>
       </c>
       <c r="F70" t="n">
-        <v>0.4087914492087612</v>
+        <v>1.304507863122988e-05</v>
       </c>
     </row>
     <row r="71">
@@ -1991,13 +1991,13 @@
         <v>0</v>
       </c>
       <c r="D71" t="n">
-        <v>0.6242174041245128</v>
+        <v>0.9951082366537252</v>
       </c>
       <c r="E71" t="n">
-        <v>0.005310075524211</v>
+        <v>0.003498065764754427</v>
       </c>
       <c r="F71" t="n">
-        <v>0.3704725203512761</v>
+        <v>0.001393697581520259</v>
       </c>
     </row>
     <row r="72">
@@ -2013,13 +2013,13 @@
         <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>0.01083386094072874</v>
+        <v>0.0004617388243043778</v>
       </c>
       <c r="E72" t="n">
-        <v>0.948482631239342</v>
+        <v>0.9995236794901492</v>
       </c>
       <c r="F72" t="n">
-        <v>0.0406835078199293</v>
+        <v>1.458168554650821e-05</v>
       </c>
     </row>
     <row r="73">
@@ -2029,19 +2029,19 @@
         </is>
       </c>
       <c r="B73" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C73" t="b">
         <v>0</v>
       </c>
       <c r="D73" t="n">
-        <v>0.2169896310865843</v>
+        <v>0.98162947401324</v>
       </c>
       <c r="E73" t="n">
-        <v>0.006192515703669351</v>
+        <v>0.01731385881451784</v>
       </c>
       <c r="F73" t="n">
-        <v>0.7768178532097463</v>
+        <v>0.001056667172242314</v>
       </c>
     </row>
     <row r="74">
@@ -2057,13 +2057,13 @@
         <v>0</v>
       </c>
       <c r="D74" t="n">
-        <v>0.6919623518553489</v>
+        <v>0.9801307738593497</v>
       </c>
       <c r="E74" t="n">
-        <v>0.02627844625266072</v>
+        <v>0.005123076612597798</v>
       </c>
       <c r="F74" t="n">
-        <v>0.2817592018919903</v>
+        <v>0.01474614952805243</v>
       </c>
     </row>
     <row r="75">
@@ -2073,19 +2073,19 @@
         </is>
       </c>
       <c r="B75" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C75" t="b">
         <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>0.1272333697114899</v>
+        <v>0.5603529103376412</v>
       </c>
       <c r="E75" t="n">
-        <v>0.3579358536142032</v>
+        <v>0.3741104442734032</v>
       </c>
       <c r="F75" t="n">
-        <v>0.5148307766743069</v>
+        <v>0.06553664538895544</v>
       </c>
     </row>
     <row r="76">
@@ -2101,13 +2101,13 @@
         <v>1</v>
       </c>
       <c r="D76" t="n">
-        <v>0.1609005876873317</v>
+        <v>0.03008278943221596</v>
       </c>
       <c r="E76" t="n">
-        <v>0.6701419751961047</v>
+        <v>0.9691181067856939</v>
       </c>
       <c r="F76" t="n">
-        <v>0.1689574371165635</v>
+        <v>0.000799103782090163</v>
       </c>
     </row>
     <row r="77">
@@ -2123,13 +2123,13 @@
         <v>0</v>
       </c>
       <c r="D77" t="n">
-        <v>0.7914013687737875</v>
+        <v>0.9657209584104381</v>
       </c>
       <c r="E77" t="n">
-        <v>0.02059318999315379</v>
+        <v>0.001416789699749343</v>
       </c>
       <c r="F77" t="n">
-        <v>0.1880054412330586</v>
+        <v>0.03286225188981248</v>
       </c>
     </row>
     <row r="78">
@@ -2145,13 +2145,13 @@
         <v>0</v>
       </c>
       <c r="D78" t="n">
-        <v>0.7100448687274357</v>
+        <v>0.9909024019972065</v>
       </c>
       <c r="E78" t="n">
-        <v>0.01102399765227187</v>
+        <v>0.001814313149949598</v>
       </c>
       <c r="F78" t="n">
-        <v>0.2789311336202925</v>
+        <v>0.007283284852843988</v>
       </c>
     </row>
     <row r="79">
@@ -2161,19 +2161,19 @@
         </is>
       </c>
       <c r="B79" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C79" t="b">
         <v>0</v>
       </c>
       <c r="D79" t="n">
-        <v>0.3441735243486531</v>
+        <v>0.8885667961602268</v>
       </c>
       <c r="E79" t="n">
-        <v>0.02630745984613316</v>
+        <v>0.1092659948653704</v>
       </c>
       <c r="F79" t="n">
-        <v>0.6295190158052137</v>
+        <v>0.002167208974402775</v>
       </c>
     </row>
     <row r="80">
@@ -2183,19 +2183,19 @@
         </is>
       </c>
       <c r="B80" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C80" t="b">
         <v>0</v>
       </c>
       <c r="D80" t="n">
-        <v>0.4116689566945158</v>
+        <v>0.9111140968900544</v>
       </c>
       <c r="E80" t="n">
-        <v>0.1333039050952178</v>
+        <v>0.07412602760745236</v>
       </c>
       <c r="F80" t="n">
-        <v>0.4550271382102664</v>
+        <v>0.01475987550249322</v>
       </c>
     </row>
     <row r="81">
@@ -2211,13 +2211,13 @@
         <v>0</v>
       </c>
       <c r="D81" t="n">
-        <v>0.5361167389460485</v>
+        <v>0.9884487841605062</v>
       </c>
       <c r="E81" t="n">
-        <v>0.01319308116346721</v>
+        <v>0.007784649309954952</v>
       </c>
       <c r="F81" t="n">
-        <v>0.4506901798904843</v>
+        <v>0.003766566529538814</v>
       </c>
     </row>
     <row r="82">
@@ -2233,13 +2233,13 @@
         <v>0</v>
       </c>
       <c r="D82" t="n">
-        <v>0.7440944493613181</v>
+        <v>0.9837065406159587</v>
       </c>
       <c r="E82" t="n">
-        <v>0.0213856721366123</v>
+        <v>0.004542940372289234</v>
       </c>
       <c r="F82" t="n">
-        <v>0.2345198785020697</v>
+        <v>0.01175051901175205</v>
       </c>
     </row>
     <row r="83">
@@ -2249,19 +2249,19 @@
         </is>
       </c>
       <c r="B83" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C83" t="b">
         <v>0</v>
       </c>
       <c r="D83" t="n">
-        <v>0.2993825330087291</v>
+        <v>0.9952021380065695</v>
       </c>
       <c r="E83" t="n">
-        <v>0.004679732853660914</v>
+        <v>0.002451323819144128</v>
       </c>
       <c r="F83" t="n">
-        <v>0.6959377341376101</v>
+        <v>0.002346538174286308</v>
       </c>
     </row>
     <row r="84">
@@ -2277,13 +2277,13 @@
         <v>0</v>
       </c>
       <c r="D84" t="n">
-        <v>0.6307734882687216</v>
+        <v>0.9254972317709191</v>
       </c>
       <c r="E84" t="n">
-        <v>0.08895573552486868</v>
+        <v>0.02304968358060882</v>
       </c>
       <c r="F84" t="n">
-        <v>0.2802707762064097</v>
+        <v>0.0514530846484722</v>
       </c>
     </row>
     <row r="85">
@@ -2299,13 +2299,13 @@
         <v>0</v>
       </c>
       <c r="D85" t="n">
-        <v>0.7913744548819888</v>
+        <v>0.9760161216003778</v>
       </c>
       <c r="E85" t="n">
-        <v>0.02275893036466712</v>
+        <v>0.003474905835590577</v>
       </c>
       <c r="F85" t="n">
-        <v>0.1858666147533441</v>
+        <v>0.02050897256403159</v>
       </c>
     </row>
     <row r="86">
@@ -2315,19 +2315,19 @@
         </is>
       </c>
       <c r="B86" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C86" t="b">
         <v>0</v>
       </c>
       <c r="D86" t="n">
-        <v>0.2392884230403388</v>
+        <v>0.8105964475731365</v>
       </c>
       <c r="E86" t="n">
-        <v>0.3240039298558398</v>
+        <v>0.09707558210112863</v>
       </c>
       <c r="F86" t="n">
-        <v>0.4367076471038215</v>
+        <v>0.09232797032573498</v>
       </c>
     </row>
     <row r="87">
@@ -2337,19 +2337,19 @@
         </is>
       </c>
       <c r="B87" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C87" t="b">
         <v>0</v>
       </c>
       <c r="D87" t="n">
-        <v>0.413424868946723</v>
+        <v>0.979039616671502</v>
       </c>
       <c r="E87" t="n">
-        <v>0.01182858259615258</v>
+        <v>0.0004581332443143007</v>
       </c>
       <c r="F87" t="n">
-        <v>0.5747465484571245</v>
+        <v>0.02050225008418369</v>
       </c>
     </row>
     <row r="88">
@@ -2359,19 +2359,19 @@
         </is>
       </c>
       <c r="B88" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C88" t="b">
         <v>0</v>
       </c>
       <c r="D88" t="n">
-        <v>0.4131731155869398</v>
+        <v>0.8856892421066149</v>
       </c>
       <c r="E88" t="n">
-        <v>0.04708134291982314</v>
+        <v>0.000805009552470213</v>
       </c>
       <c r="F88" t="n">
-        <v>0.5397455414932369</v>
+        <v>0.1135057483409148</v>
       </c>
     </row>
     <row r="89">
@@ -2381,19 +2381,19 @@
         </is>
       </c>
       <c r="B89" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C89" t="b">
         <v>0</v>
       </c>
       <c r="D89" t="n">
-        <v>0.3448063991186043</v>
+        <v>0.9729926050240886</v>
       </c>
       <c r="E89" t="n">
-        <v>0.01153236984596796</v>
+        <v>0.0003896314114954385</v>
       </c>
       <c r="F89" t="n">
-        <v>0.6436612310354278</v>
+        <v>0.02661776356441578</v>
       </c>
     </row>
     <row r="90">
@@ -2403,19 +2403,19 @@
         </is>
       </c>
       <c r="B90" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C90" t="b">
         <v>0</v>
       </c>
       <c r="D90" t="n">
-        <v>0.1694957741210917</v>
+        <v>0.9764367646328375</v>
       </c>
       <c r="E90" t="n">
-        <v>0.01017082420259059</v>
+        <v>0.000858308874160191</v>
       </c>
       <c r="F90" t="n">
-        <v>0.8203334016763177</v>
+        <v>0.0227049264930023</v>
       </c>
     </row>
     <row r="91">
@@ -2431,13 +2431,13 @@
         <v>1</v>
       </c>
       <c r="D91" t="n">
-        <v>0.5247605379353433</v>
+        <v>0.8806650594323798</v>
       </c>
       <c r="E91" t="n">
-        <v>0.1076562607444456</v>
+        <v>0.005851423730362198</v>
       </c>
       <c r="F91" t="n">
-        <v>0.3675832013202111</v>
+        <v>0.1134835168372581</v>
       </c>
     </row>
     <row r="92">
@@ -2453,13 +2453,13 @@
         <v>0</v>
       </c>
       <c r="D92" t="n">
-        <v>0.6301122819212948</v>
+        <v>0.9170984004967904</v>
       </c>
       <c r="E92" t="n">
-        <v>0.01973539919285075</v>
+        <v>0.0002168353429721308</v>
       </c>
       <c r="F92" t="n">
-        <v>0.3501523188858544</v>
+        <v>0.08268476416023747</v>
       </c>
     </row>
     <row r="93">
@@ -2475,13 +2475,13 @@
         <v>0</v>
       </c>
       <c r="D93" t="n">
-        <v>0.4010781816463528</v>
+        <v>0.8735503662115406</v>
       </c>
       <c r="E93" t="n">
-        <v>0.2131986067418654</v>
+        <v>0.02690711922457978</v>
       </c>
       <c r="F93" t="n">
-        <v>0.3857232116117817</v>
+        <v>0.09954251456387968</v>
       </c>
     </row>
     <row r="94">
@@ -2491,19 +2491,19 @@
         </is>
       </c>
       <c r="B94" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C94" t="b">
         <v>0</v>
       </c>
       <c r="D94" t="n">
-        <v>0.3497843837971528</v>
+        <v>0.9037667791601526</v>
       </c>
       <c r="E94" t="n">
-        <v>0.1743168983543055</v>
+        <v>0.02453224917702694</v>
       </c>
       <c r="F94" t="n">
-        <v>0.4758987178485417</v>
+        <v>0.07170097166282059</v>
       </c>
     </row>
     <row r="95">
@@ -2513,19 +2513,19 @@
         </is>
       </c>
       <c r="B95" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C95" t="b">
         <v>0</v>
       </c>
       <c r="D95" t="n">
-        <v>0.4021833063407701</v>
+        <v>0.9042312450939256</v>
       </c>
       <c r="E95" t="n">
-        <v>0.03015102940967977</v>
+        <v>0.0007858561339937125</v>
       </c>
       <c r="F95" t="n">
-        <v>0.5676656642495501</v>
+        <v>0.09498289877208067</v>
       </c>
     </row>
     <row r="96">
@@ -2541,13 +2541,13 @@
         <v>0</v>
       </c>
       <c r="D96" t="n">
-        <v>0.5047239293957929</v>
+        <v>0.8806450698689116</v>
       </c>
       <c r="E96" t="n">
-        <v>0.1324345791253611</v>
+        <v>0.01097338014294565</v>
       </c>
       <c r="F96" t="n">
-        <v>0.362841491478846</v>
+        <v>0.1083815499881429</v>
       </c>
     </row>
     <row r="97">
@@ -2557,19 +2557,19 @@
         </is>
       </c>
       <c r="B97" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C97" t="b">
         <v>0</v>
       </c>
       <c r="D97" t="n">
-        <v>0.3165557345750407</v>
+        <v>0.8541111969769104</v>
       </c>
       <c r="E97" t="n">
-        <v>0.2423038014793353</v>
+        <v>0.07481738916773506</v>
       </c>
       <c r="F97" t="n">
-        <v>0.4411404639456241</v>
+        <v>0.07107141385535448</v>
       </c>
     </row>
     <row r="98">
@@ -2579,19 +2579,19 @@
         </is>
       </c>
       <c r="B98" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C98" t="b">
         <v>0</v>
       </c>
       <c r="D98" t="n">
-        <v>0.2111653239933117</v>
+        <v>0.8116383842828304</v>
       </c>
       <c r="E98" t="n">
-        <v>0.2217951963407293</v>
+        <v>0.1528861253402349</v>
       </c>
       <c r="F98" t="n">
-        <v>0.5670394796659591</v>
+        <v>0.03547549037693475</v>
       </c>
     </row>
     <row r="99">
@@ -2607,13 +2607,13 @@
         <v>0</v>
       </c>
       <c r="D99" t="n">
-        <v>0.5868768418244803</v>
+        <v>0.9443706895584179</v>
       </c>
       <c r="E99" t="n">
-        <v>0.02724346267843604</v>
+        <v>0.0006505074949609821</v>
       </c>
       <c r="F99" t="n">
-        <v>0.3858796954970835</v>
+        <v>0.05497880294662107</v>
       </c>
     </row>
     <row r="100">
@@ -2629,13 +2629,13 @@
         <v>1</v>
       </c>
       <c r="D100" t="n">
-        <v>0.6917609145661818</v>
+        <v>0.9759847224101345</v>
       </c>
       <c r="E100" t="n">
-        <v>0.04319565258779271</v>
+        <v>0.01243438414780519</v>
       </c>
       <c r="F100" t="n">
-        <v>0.2650434328460256</v>
+        <v>0.01158089344206023</v>
       </c>
     </row>
     <row r="101">
@@ -2651,13 +2651,13 @@
         <v>1</v>
       </c>
       <c r="D101" t="n">
-        <v>0.7165379005921519</v>
+        <v>0.9345960240540114</v>
       </c>
       <c r="E101" t="n">
-        <v>0.07684719035214374</v>
+        <v>0.01946712958741765</v>
       </c>
       <c r="F101" t="n">
-        <v>0.2066149090557043</v>
+        <v>0.0459368463585708</v>
       </c>
     </row>
     <row r="102">
@@ -2667,19 +2667,19 @@
         </is>
       </c>
       <c r="B102" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C102" t="b">
         <v>0</v>
       </c>
       <c r="D102" t="n">
-        <v>0.2491611975638301</v>
+        <v>0.9496422030955576</v>
       </c>
       <c r="E102" t="n">
-        <v>0.0300343976302341</v>
+        <v>0.04781837078155306</v>
       </c>
       <c r="F102" t="n">
-        <v>0.7208044048059358</v>
+        <v>0.002539426122889295</v>
       </c>
     </row>
     <row r="103">
@@ -2689,19 +2689,19 @@
         </is>
       </c>
       <c r="B103" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C103" t="b">
         <v>0</v>
       </c>
       <c r="D103" t="n">
-        <v>0.2892272874651778</v>
+        <v>0.9521155568658883</v>
       </c>
       <c r="E103" t="n">
-        <v>0.03703476665054005</v>
+        <v>0.04381421050786202</v>
       </c>
       <c r="F103" t="n">
-        <v>0.6737379458842822</v>
+        <v>0.004070232626249756</v>
       </c>
     </row>
     <row r="104">
@@ -2717,13 +2717,13 @@
         <v>1</v>
       </c>
       <c r="D104" t="n">
-        <v>0.1710881819891927</v>
+        <v>0.2144574170206051</v>
       </c>
       <c r="E104" t="n">
-        <v>0.6298466486447568</v>
+        <v>0.7745941593649132</v>
       </c>
       <c r="F104" t="n">
-        <v>0.1990651693660506</v>
+        <v>0.01094842361448179</v>
       </c>
     </row>
     <row r="105">
@@ -2739,13 +2739,13 @@
         <v>0</v>
       </c>
       <c r="D105" t="n">
-        <v>0.4960796181497802</v>
+        <v>0.9630148659294272</v>
       </c>
       <c r="E105" t="n">
-        <v>0.03461347699296659</v>
+        <v>0.003023039159706456</v>
       </c>
       <c r="F105" t="n">
-        <v>0.4693069048572532</v>
+        <v>0.03396209491086625</v>
       </c>
     </row>
     <row r="106">
@@ -2761,13 +2761,13 @@
         <v>0</v>
       </c>
       <c r="D106" t="n">
-        <v>0.5286563328941989</v>
+        <v>0.9693694237687525</v>
       </c>
       <c r="E106" t="n">
-        <v>0.04854065065027637</v>
+        <v>0.006590384051288431</v>
       </c>
       <c r="F106" t="n">
-        <v>0.4228030164555248</v>
+        <v>0.02404019217995894</v>
       </c>
     </row>
     <row r="107">
@@ -2783,13 +2783,13 @@
         <v>0</v>
       </c>
       <c r="D107" t="n">
-        <v>0.5392553513477729</v>
+        <v>0.877020148201923</v>
       </c>
       <c r="E107" t="n">
-        <v>0.04091893009213814</v>
+        <v>0.0008378085906247568</v>
       </c>
       <c r="F107" t="n">
-        <v>0.4198257185600888</v>
+        <v>0.1221420432074522</v>
       </c>
     </row>
     <row r="108">
@@ -2805,13 +2805,13 @@
         <v>0</v>
       </c>
       <c r="D108" t="n">
-        <v>0.4081322525147662</v>
+        <v>0.8327847331567724</v>
       </c>
       <c r="E108" t="n">
-        <v>0.2158274926290258</v>
+        <v>0.03822605863387918</v>
       </c>
       <c r="F108" t="n">
-        <v>0.3760402548562079</v>
+        <v>0.1289892082093485</v>
       </c>
     </row>
     <row r="109">
@@ -2821,19 +2821,19 @@
         </is>
       </c>
       <c r="B109" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C109" t="b">
         <v>0</v>
       </c>
       <c r="D109" t="n">
-        <v>0.2721184529568857</v>
+        <v>0.9618383335749933</v>
       </c>
       <c r="E109" t="n">
-        <v>0.02917678455759859</v>
+        <v>0.003624637894153659</v>
       </c>
       <c r="F109" t="n">
-        <v>0.6987047624855157</v>
+        <v>0.03453702853085314</v>
       </c>
     </row>
     <row r="110">
@@ -2843,19 +2843,19 @@
         </is>
       </c>
       <c r="B110" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C110" t="b">
         <v>0</v>
       </c>
       <c r="D110" t="n">
-        <v>0.1983195872322853</v>
+        <v>0.9654198734810219</v>
       </c>
       <c r="E110" t="n">
-        <v>0.03753670501299938</v>
+        <v>0.0115045634920271</v>
       </c>
       <c r="F110" t="n">
-        <v>0.7641437077547152</v>
+        <v>0.02307556302695107</v>
       </c>
     </row>
     <row r="111">
@@ -2871,13 +2871,13 @@
         <v>0</v>
       </c>
       <c r="D111" t="n">
-        <v>0.7348464050428668</v>
+        <v>0.9391566773798965</v>
       </c>
       <c r="E111" t="n">
-        <v>0.06739770592178423</v>
+        <v>0.0190676493277276</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1977558890353489</v>
+        <v>0.04177567329237613</v>
       </c>
     </row>
     <row r="112">
@@ -2887,19 +2887,19 @@
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C112" t="b">
         <v>1</v>
       </c>
       <c r="D112" t="n">
-        <v>0.2687837263580748</v>
+        <v>0.7048749134979005</v>
       </c>
       <c r="E112" t="n">
-        <v>0.2090586258329865</v>
+        <v>0.015579560155382</v>
       </c>
       <c r="F112" t="n">
-        <v>0.5221576478089386</v>
+        <v>0.2795455263467175</v>
       </c>
     </row>
     <row r="113">
@@ -2915,13 +2915,13 @@
         <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>0.5353482898424536</v>
+        <v>0.7850646761746903</v>
       </c>
       <c r="E113" t="n">
-        <v>0.1042281722523922</v>
+        <v>0.003123857571621328</v>
       </c>
       <c r="F113" t="n">
-        <v>0.3604235379051542</v>
+        <v>0.2118114662536883</v>
       </c>
     </row>
     <row r="114">
@@ -2931,19 +2931,19 @@
         </is>
       </c>
       <c r="B114" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C114" t="b">
         <v>0</v>
       </c>
       <c r="D114" t="n">
-        <v>0.4260395355887231</v>
+        <v>0.9612021913548371</v>
       </c>
       <c r="E114" t="n">
-        <v>0.02924650046815064</v>
+        <v>0.003032809065535023</v>
       </c>
       <c r="F114" t="n">
-        <v>0.5447139639431263</v>
+        <v>0.03576499957962781</v>
       </c>
     </row>
     <row r="115">
@@ -2953,19 +2953,19 @@
         </is>
       </c>
       <c r="B115" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C115" t="b">
         <v>0</v>
       </c>
       <c r="D115" t="n">
-        <v>0.186579024730413</v>
+        <v>0.6563290896087806</v>
       </c>
       <c r="E115" t="n">
-        <v>0.1116993840864082</v>
+        <v>0.00366851556384724</v>
       </c>
       <c r="F115" t="n">
-        <v>0.7017215911831789</v>
+        <v>0.3400023948273723</v>
       </c>
     </row>
     <row r="116">
@@ -2981,13 +2981,13 @@
         <v>0</v>
       </c>
       <c r="D116" t="n">
-        <v>0.1592896865508309</v>
+        <v>0.1542572229794522</v>
       </c>
       <c r="E116" t="n">
-        <v>0.2076010166831593</v>
+        <v>0.0002062437175339977</v>
       </c>
       <c r="F116" t="n">
-        <v>0.6331092967660098</v>
+        <v>0.8455365333030137</v>
       </c>
     </row>
     <row r="117">
@@ -2997,19 +2997,19 @@
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C117" t="b">
         <v>0</v>
       </c>
       <c r="D117" t="n">
-        <v>0.3355010998433929</v>
+        <v>0.8200952489560112</v>
       </c>
       <c r="E117" t="n">
-        <v>0.07213097346432017</v>
+        <v>0.001554378436421757</v>
       </c>
       <c r="F117" t="n">
-        <v>0.592367926692287</v>
+        <v>0.178350372607567</v>
       </c>
     </row>
     <row r="118">
@@ -3019,19 +3019,19 @@
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C118" t="b">
         <v>1</v>
       </c>
       <c r="D118" t="n">
-        <v>0.4289497234883349</v>
+        <v>0.8296355833654192</v>
       </c>
       <c r="E118" t="n">
-        <v>0.07852026325293671</v>
+        <v>0.002511099749325825</v>
       </c>
       <c r="F118" t="n">
-        <v>0.4925300132587284</v>
+        <v>0.167853316885255</v>
       </c>
     </row>
     <row r="119">
@@ -3047,13 +3047,13 @@
         <v>0</v>
       </c>
       <c r="D119" t="n">
-        <v>0.4527988295209658</v>
+        <v>0.8308985637690545</v>
       </c>
       <c r="E119" t="n">
-        <v>0.1055840667383941</v>
+        <v>0.003406536480382001</v>
       </c>
       <c r="F119" t="n">
-        <v>0.44161710374064</v>
+        <v>0.1656948997505636</v>
       </c>
     </row>
     <row r="120">
@@ -3063,19 +3063,19 @@
         </is>
       </c>
       <c r="B120" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C120" t="b">
         <v>0</v>
       </c>
       <c r="D120" t="n">
-        <v>0.2621873337367419</v>
+        <v>0.9302935351611223</v>
       </c>
       <c r="E120" t="n">
-        <v>0.05607659510127148</v>
+        <v>0.004882518126294105</v>
       </c>
       <c r="F120" t="n">
-        <v>0.6817360711619868</v>
+        <v>0.06482394671258356</v>
       </c>
     </row>
     <row r="121">
@@ -3085,19 +3085,19 @@
         </is>
       </c>
       <c r="B121" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C121" t="b">
         <v>0</v>
       </c>
       <c r="D121" t="n">
-        <v>0.4297509222037928</v>
+        <v>0.9263043570359006</v>
       </c>
       <c r="E121" t="n">
-        <v>0.03494559832828747</v>
+        <v>0.001516575770943957</v>
       </c>
       <c r="F121" t="n">
-        <v>0.5353034794679198</v>
+        <v>0.07217906719315549</v>
       </c>
     </row>
     <row r="122">
@@ -3113,13 +3113,13 @@
         <v>0</v>
       </c>
       <c r="D122" t="n">
-        <v>0.4714621474259513</v>
+        <v>0.8889994903794455</v>
       </c>
       <c r="E122" t="n">
-        <v>0.09520119413419444</v>
+        <v>0.005949363307959431</v>
       </c>
       <c r="F122" t="n">
-        <v>0.4333366584398544</v>
+        <v>0.1050511463125951</v>
       </c>
     </row>
     <row r="123">
@@ -3129,19 +3129,19 @@
         </is>
       </c>
       <c r="B123" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C123" t="b">
         <v>0</v>
       </c>
       <c r="D123" t="n">
-        <v>0.2609090058636013</v>
+        <v>0.9141541730407228</v>
       </c>
       <c r="E123" t="n">
-        <v>0.1214127904868959</v>
+        <v>0.02971314405827776</v>
       </c>
       <c r="F123" t="n">
-        <v>0.6176782036495029</v>
+        <v>0.05613268290099938</v>
       </c>
     </row>
     <row r="124">
@@ -3151,19 +3151,19 @@
         </is>
       </c>
       <c r="B124" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C124" t="b">
         <v>0</v>
       </c>
       <c r="D124" t="n">
-        <v>0.3528443496885179</v>
+        <v>0.8968565335359895</v>
       </c>
       <c r="E124" t="n">
-        <v>0.1303859972462292</v>
+        <v>0.02731151722577049</v>
       </c>
       <c r="F124" t="n">
-        <v>0.5167696530652529</v>
+        <v>0.07583194923823994</v>
       </c>
     </row>
     <row r="125">
@@ -3173,19 +3173,19 @@
         </is>
       </c>
       <c r="B125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C125" t="b">
         <v>0</v>
       </c>
       <c r="D125" t="n">
-        <v>0.1901722198160366</v>
+        <v>0.9715065232820778</v>
       </c>
       <c r="E125" t="n">
-        <v>0.0283764360279287</v>
+        <v>0.0104636402294045</v>
       </c>
       <c r="F125" t="n">
-        <v>0.7814513441560348</v>
+        <v>0.01802983648851773</v>
       </c>
     </row>
     <row r="126">
@@ -3195,19 +3195,19 @@
         </is>
       </c>
       <c r="B126" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C126" t="b">
         <v>0</v>
       </c>
       <c r="D126" t="n">
-        <v>0.02468215822882497</v>
+        <v>0.9942102656703328</v>
       </c>
       <c r="E126" t="n">
-        <v>0.0006142798290983953</v>
+        <v>0.000158156440718052</v>
       </c>
       <c r="F126" t="n">
-        <v>0.9747035619420766</v>
+        <v>0.005631577888949149</v>
       </c>
     </row>
     <row r="127">
@@ -3217,19 +3217,19 @@
         </is>
       </c>
       <c r="B127" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C127" t="b">
         <v>0</v>
       </c>
       <c r="D127" t="n">
-        <v>0.2785407812512089</v>
+        <v>0.7993014513370538</v>
       </c>
       <c r="E127" t="n">
-        <v>0.2438607235326041</v>
+        <v>0.03406356085319017</v>
       </c>
       <c r="F127" t="n">
-        <v>0.477598495216187</v>
+        <v>0.166634987809756</v>
       </c>
     </row>
     <row r="128">
@@ -3239,19 +3239,19 @@
         </is>
       </c>
       <c r="B128" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C128" t="b">
         <v>0</v>
       </c>
       <c r="D128" t="n">
-        <v>0.4247416985943584</v>
+        <v>0.8452324045984563</v>
       </c>
       <c r="E128" t="n">
-        <v>0.02836071315914371</v>
+        <v>0.0002619243549266664</v>
       </c>
       <c r="F128" t="n">
-        <v>0.5468975882464979</v>
+        <v>0.1545056710466171</v>
       </c>
     </row>
     <row r="129">
@@ -3261,19 +3261,19 @@
         </is>
       </c>
       <c r="B129" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C129" t="b">
         <v>0</v>
       </c>
       <c r="D129" t="n">
-        <v>0.182318863051148</v>
+        <v>0.9553926423332441</v>
       </c>
       <c r="E129" t="n">
-        <v>0.05275572291449081</v>
+        <v>0.01819006909873255</v>
       </c>
       <c r="F129" t="n">
-        <v>0.7649254140343611</v>
+        <v>0.02641728856802352</v>
       </c>
     </row>
     <row r="130">
@@ -3283,19 +3283,19 @@
         </is>
       </c>
       <c r="B130" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C130" t="b">
         <v>0</v>
       </c>
       <c r="D130" t="n">
-        <v>0.3938867744171579</v>
+        <v>0.9413700065282713</v>
       </c>
       <c r="E130" t="n">
-        <v>0.0436745420807915</v>
+        <v>0.003404727148343327</v>
       </c>
       <c r="F130" t="n">
-        <v>0.5624386835020506</v>
+        <v>0.05522526632338537</v>
       </c>
     </row>
     <row r="131">
@@ -3305,19 +3305,19 @@
         </is>
       </c>
       <c r="B131" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C131" t="b">
         <v>0</v>
       </c>
       <c r="D131" t="n">
-        <v>0.3580881714950293</v>
+        <v>0.9312788333692414</v>
       </c>
       <c r="E131" t="n">
-        <v>0.06538720607975516</v>
+        <v>0.005594392398582358</v>
       </c>
       <c r="F131" t="n">
-        <v>0.5765246224252156</v>
+        <v>0.06312677423217626</v>
       </c>
     </row>
     <row r="132">
@@ -3333,13 +3333,13 @@
         <v>0</v>
       </c>
       <c r="D132" t="n">
-        <v>0.5192643152092675</v>
+        <v>0.9504611994459593</v>
       </c>
       <c r="E132" t="n">
-        <v>0.04220458754130356</v>
+        <v>0.004612086368860455</v>
       </c>
       <c r="F132" t="n">
-        <v>0.438531097249429</v>
+        <v>0.04492671418518016</v>
       </c>
     </row>
     <row r="133">
@@ -3349,19 +3349,19 @@
         </is>
       </c>
       <c r="B133" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C133" t="b">
         <v>0</v>
       </c>
       <c r="D133" t="n">
-        <v>0.3419922542871164</v>
+        <v>0.9078785678156764</v>
       </c>
       <c r="E133" t="n">
-        <v>0.07228524078318264</v>
+        <v>0.01218530020343705</v>
       </c>
       <c r="F133" t="n">
-        <v>0.5857225049297009</v>
+        <v>0.07993613198088653</v>
       </c>
     </row>
     <row r="134">
@@ -3371,19 +3371,19 @@
         </is>
       </c>
       <c r="B134" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C134" t="b">
         <v>0</v>
       </c>
       <c r="D134" t="n">
-        <v>0.2849857481797156</v>
+        <v>0.98217849265325</v>
       </c>
       <c r="E134" t="n">
-        <v>0.0149740892812601</v>
+        <v>0.003838241826418718</v>
       </c>
       <c r="F134" t="n">
-        <v>0.7000401625390243</v>
+        <v>0.01398326552033123</v>
       </c>
     </row>
     <row r="135">
@@ -3399,13 +3399,13 @@
         <v>0</v>
       </c>
       <c r="D135" t="n">
-        <v>0.09931136287829975</v>
+        <v>0.1520874890712592</v>
       </c>
       <c r="E135" t="n">
-        <v>0.7160779403455912</v>
+        <v>0.8207816588027053</v>
       </c>
       <c r="F135" t="n">
-        <v>0.1846106967761089</v>
+        <v>0.02713085212603564</v>
       </c>
     </row>
     <row r="136">
@@ -3415,19 +3415,19 @@
         </is>
       </c>
       <c r="B136" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C136" t="b">
         <v>0</v>
       </c>
       <c r="D136" t="n">
-        <v>0.1565774002125374</v>
+        <v>0.7212196156158054</v>
       </c>
       <c r="E136" t="n">
-        <v>0.141970690888698</v>
+        <v>0.003535312204726999</v>
       </c>
       <c r="F136" t="n">
-        <v>0.7014519088987646</v>
+        <v>0.2752450721794676</v>
       </c>
     </row>
     <row r="137">
@@ -3437,19 +3437,19 @@
         </is>
       </c>
       <c r="B137" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C137" t="b">
         <v>0</v>
       </c>
       <c r="D137" t="n">
-        <v>0.3037372877799791</v>
+        <v>0.88472761566532</v>
       </c>
       <c r="E137" t="n">
-        <v>0.1530088603713998</v>
+        <v>0.09568079500380111</v>
       </c>
       <c r="F137" t="n">
-        <v>0.5432538518486211</v>
+        <v>0.01959158933087895</v>
       </c>
     </row>
     <row r="138">
@@ -3459,19 +3459,19 @@
         </is>
       </c>
       <c r="B138" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C138" t="b">
         <v>0</v>
       </c>
       <c r="D138" t="n">
-        <v>0.3009135052099005</v>
+        <v>0.9593666880498782</v>
       </c>
       <c r="E138" t="n">
-        <v>0.02065987421248968</v>
+        <v>0.00126454998397832</v>
       </c>
       <c r="F138" t="n">
-        <v>0.6784266205776098</v>
+        <v>0.03936876196614342</v>
       </c>
     </row>
     <row r="139">
@@ -3481,19 +3481,19 @@
         </is>
       </c>
       <c r="B139" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C139" t="b">
         <v>0</v>
       </c>
       <c r="D139" t="n">
-        <v>0.3023433902829706</v>
+        <v>0.768769211004851</v>
       </c>
       <c r="E139" t="n">
-        <v>0.1478553680098198</v>
+        <v>0.006540945938998934</v>
       </c>
       <c r="F139" t="n">
-        <v>0.5498012417072096</v>
+        <v>0.22468984305615</v>
       </c>
     </row>
     <row r="140">
@@ -3503,19 +3503,19 @@
         </is>
       </c>
       <c r="B140" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C140" t="b">
         <v>0</v>
       </c>
       <c r="D140" t="n">
-        <v>0.2451288989900603</v>
+        <v>0.734760123951594</v>
       </c>
       <c r="E140" t="n">
-        <v>0.08548732246544648</v>
+        <v>0.0007364213527902134</v>
       </c>
       <c r="F140" t="n">
-        <v>0.6693837785444934</v>
+        <v>0.2645034546956158</v>
       </c>
     </row>
     <row r="141">
@@ -3525,19 +3525,19 @@
         </is>
       </c>
       <c r="B141" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C141" t="b">
         <v>0</v>
       </c>
       <c r="D141" t="n">
-        <v>0.04107959874295187</v>
+        <v>0.6780608121772472</v>
       </c>
       <c r="E141" t="n">
-        <v>0.01052259711038264</v>
+        <v>9.807717706036487e-05</v>
       </c>
       <c r="F141" t="n">
-        <v>0.9483978041466655</v>
+        <v>0.3218411106456924</v>
       </c>
     </row>
     <row r="142">
@@ -3547,19 +3547,19 @@
         </is>
       </c>
       <c r="B142" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C142" t="b">
         <v>0</v>
       </c>
       <c r="D142" t="n">
-        <v>0.1701312903757782</v>
+        <v>0.9143512250003382</v>
       </c>
       <c r="E142" t="n">
-        <v>0.02283819491828568</v>
+        <v>0.0005244545118092687</v>
       </c>
       <c r="F142" t="n">
-        <v>0.8070305147059361</v>
+        <v>0.08512432048785264</v>
       </c>
     </row>
     <row r="143">
@@ -3569,19 +3569,19 @@
         </is>
       </c>
       <c r="B143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C143" t="b">
         <v>0</v>
       </c>
       <c r="D143" t="n">
-        <v>0.04990829430904392</v>
+        <v>0.5335298630594211</v>
       </c>
       <c r="E143" t="n">
-        <v>0.5455411327015514</v>
+        <v>0.04818397305929762</v>
       </c>
       <c r="F143" t="n">
-        <v>0.4045505729894047</v>
+        <v>0.4182861638812813</v>
       </c>
     </row>
     <row r="144">
@@ -3597,13 +3597,13 @@
         <v>1</v>
       </c>
       <c r="D144" t="n">
-        <v>0.2160027351567893</v>
+        <v>0.1443578916117968</v>
       </c>
       <c r="E144" t="n">
-        <v>0.05406866643260889</v>
+        <v>4.085099451682151e-06</v>
       </c>
       <c r="F144" t="n">
-        <v>0.7299285984106019</v>
+        <v>0.8556380232887515</v>
       </c>
     </row>
     <row r="145">
@@ -3613,19 +3613,19 @@
         </is>
       </c>
       <c r="B145" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C145" t="b">
         <v>0</v>
       </c>
       <c r="D145" t="n">
-        <v>0.2274989585175337</v>
+        <v>0.8767557851163448</v>
       </c>
       <c r="E145" t="n">
-        <v>0.03081446649868115</v>
+        <v>0.0004565776204349097</v>
       </c>
       <c r="F145" t="n">
-        <v>0.7416865749837851</v>
+        <v>0.1227876372632202</v>
       </c>
     </row>
     <row r="146">
@@ -3635,19 +3635,19 @@
         </is>
       </c>
       <c r="B146" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C146" t="b">
         <v>1</v>
       </c>
       <c r="D146" t="n">
-        <v>0.2329014762378219</v>
+        <v>0.6048054475816421</v>
       </c>
       <c r="E146" t="n">
-        <v>0.3695141408736883</v>
+        <v>0.0177156501937663</v>
       </c>
       <c r="F146" t="n">
-        <v>0.3975843828884897</v>
+        <v>0.3774789022245916</v>
       </c>
     </row>
     <row r="147">
@@ -3663,13 +3663,13 @@
         <v>1</v>
       </c>
       <c r="D147" t="n">
-        <v>0.5611466891467558</v>
+        <v>0.8661044944409373</v>
       </c>
       <c r="E147" t="n">
-        <v>0.07046329065276505</v>
+        <v>0.002533548098472692</v>
       </c>
       <c r="F147" t="n">
-        <v>0.3683900202004792</v>
+        <v>0.13136195746059</v>
       </c>
     </row>
     <row r="148">
@@ -3679,19 +3679,19 @@
         </is>
       </c>
       <c r="B148" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C148" t="b">
         <v>0</v>
       </c>
       <c r="D148" t="n">
-        <v>0.4595289828560655</v>
+        <v>0.9068382384670988</v>
       </c>
       <c r="E148" t="n">
-        <v>0.07810825795843836</v>
+        <v>0.004429337301642294</v>
       </c>
       <c r="F148" t="n">
-        <v>0.4623627591854961</v>
+        <v>0.08873242423125891</v>
       </c>
     </row>
     <row r="149">
@@ -3701,19 +3701,19 @@
         </is>
       </c>
       <c r="B149" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C149" t="b">
         <v>0</v>
       </c>
       <c r="D149" t="n">
-        <v>0.165186384458828</v>
+        <v>0.5898305786573022</v>
       </c>
       <c r="E149" t="n">
-        <v>0.4946940338418792</v>
+        <v>0.3444184812151421</v>
       </c>
       <c r="F149" t="n">
-        <v>0.3401195816992928</v>
+        <v>0.06575094012755563</v>
       </c>
     </row>
     <row r="150">
@@ -3729,13 +3729,13 @@
         <v>0</v>
       </c>
       <c r="D150" t="n">
-        <v>0.4056069037995457</v>
+        <v>0.6257180294134129</v>
       </c>
       <c r="E150" t="n">
-        <v>0.293573124745757</v>
+        <v>0.3289142262101018</v>
       </c>
       <c r="F150" t="n">
-        <v>0.3008199714546974</v>
+        <v>0.04536774437648533</v>
       </c>
     </row>
     <row r="151">
@@ -3751,13 +3751,13 @@
         <v>0</v>
       </c>
       <c r="D151" t="n">
-        <v>0.5898431808698368</v>
+        <v>0.8429924318110179</v>
       </c>
       <c r="E151" t="n">
-        <v>0.04897090966175562</v>
+        <v>0.0007041868821196427</v>
       </c>
       <c r="F151" t="n">
-        <v>0.3611859094684077</v>
+        <v>0.1563033813068626</v>
       </c>
     </row>
     <row r="152">
@@ -3773,13 +3773,13 @@
         <v>0</v>
       </c>
       <c r="D152" t="n">
-        <v>0.06243471717188932</v>
+        <v>0.1109129818771477</v>
       </c>
       <c r="E152" t="n">
-        <v>0.7589880847185476</v>
+        <v>0.866567537250205</v>
       </c>
       <c r="F152" t="n">
-        <v>0.178577198109563</v>
+        <v>0.02251948087264725</v>
       </c>
     </row>
     <row r="153">
@@ -3789,19 +3789,19 @@
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C153" t="b">
         <v>0</v>
       </c>
       <c r="D153" t="n">
-        <v>0.3410755751177637</v>
+        <v>0.7444303392240976</v>
       </c>
       <c r="E153" t="n">
-        <v>0.2628354464431665</v>
+        <v>0.05742082659752976</v>
       </c>
       <c r="F153" t="n">
-        <v>0.3960889784390698</v>
+        <v>0.1981488341783727</v>
       </c>
     </row>
     <row r="154">
@@ -3811,19 +3811,19 @@
         </is>
       </c>
       <c r="B154" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C154" t="b">
         <v>0</v>
       </c>
       <c r="D154" t="n">
-        <v>0.1428281179613603</v>
+        <v>0.6557435590361285</v>
       </c>
       <c r="E154" t="n">
-        <v>0.4683779832755305</v>
+        <v>0.06769992870720998</v>
       </c>
       <c r="F154" t="n">
-        <v>0.3887938987631092</v>
+        <v>0.2765565122566614</v>
       </c>
     </row>
     <row r="155">
@@ -3833,19 +3833,19 @@
         </is>
       </c>
       <c r="B155" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C155" t="b">
         <v>0</v>
       </c>
       <c r="D155" t="n">
-        <v>0.2413070528634391</v>
+        <v>0.8601640846660893</v>
       </c>
       <c r="E155" t="n">
-        <v>0.09979130073179837</v>
+        <v>0.007685070805775534</v>
       </c>
       <c r="F155" t="n">
-        <v>0.6589016464047625</v>
+        <v>0.1321508445281352</v>
       </c>
     </row>
     <row r="156">
@@ -3855,19 +3855,19 @@
         </is>
       </c>
       <c r="B156" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C156" t="b">
         <v>0</v>
       </c>
       <c r="D156" t="n">
-        <v>0.2949254609062126</v>
+        <v>0.8110976479031263</v>
       </c>
       <c r="E156" t="n">
-        <v>0.2602486334649025</v>
+        <v>0.04597997890409975</v>
       </c>
       <c r="F156" t="n">
-        <v>0.444825905628885</v>
+        <v>0.1429223731927738</v>
       </c>
     </row>
     <row r="157">
@@ -3883,13 +3883,13 @@
         <v>0</v>
       </c>
       <c r="D157" t="n">
-        <v>0.197283656210692</v>
+        <v>0.3652087526005567</v>
       </c>
       <c r="E157" t="n">
-        <v>0.4702716341707417</v>
+        <v>0.596306730604539</v>
       </c>
       <c r="F157" t="n">
-        <v>0.3324447096185663</v>
+        <v>0.03848451679490424</v>
       </c>
     </row>
     <row r="158">
@@ -3899,19 +3899,19 @@
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C158" t="b">
         <v>1</v>
       </c>
       <c r="D158" t="n">
-        <v>0.3094747352598711</v>
+        <v>0.8091562416758987</v>
       </c>
       <c r="E158" t="n">
-        <v>0.2158256894385251</v>
+        <v>0.0196454326590326</v>
       </c>
       <c r="F158" t="n">
-        <v>0.4746995753016038</v>
+        <v>0.1711983256650686</v>
       </c>
     </row>
     <row r="159">
@@ -3921,19 +3921,19 @@
         </is>
       </c>
       <c r="B159" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C159" t="b">
         <v>0</v>
       </c>
       <c r="D159" t="n">
-        <v>0.1843251830772594</v>
+        <v>0.4902869724351639</v>
       </c>
       <c r="E159" t="n">
-        <v>0.470406617161479</v>
+        <v>0.4092646903572787</v>
       </c>
       <c r="F159" t="n">
-        <v>0.3452681997612616</v>
+        <v>0.1004483372075574</v>
       </c>
     </row>
     <row r="160">
@@ -3943,19 +3943,19 @@
         </is>
       </c>
       <c r="B160" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C160" t="b">
         <v>0</v>
       </c>
       <c r="D160" t="n">
-        <v>0.2130705698847228</v>
+        <v>0.7530697384890563</v>
       </c>
       <c r="E160" t="n">
-        <v>0.2203038875381343</v>
+        <v>0.02072040048159213</v>
       </c>
       <c r="F160" t="n">
-        <v>0.5666255425771428</v>
+        <v>0.2262098610293516</v>
       </c>
     </row>
     <row r="161">
@@ -3965,19 +3965,19 @@
         </is>
       </c>
       <c r="B161" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C161" t="b">
         <v>1</v>
       </c>
       <c r="D161" t="n">
-        <v>0.2360244119250482</v>
+        <v>0.67217096003495</v>
       </c>
       <c r="E161" t="n">
-        <v>0.4063664296592963</v>
+        <v>0.2697643048105642</v>
       </c>
       <c r="F161" t="n">
-        <v>0.3576091584156555</v>
+        <v>0.0580647351544858</v>
       </c>
     </row>
     <row r="162">
@@ -3987,19 +3987,19 @@
         </is>
       </c>
       <c r="B162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C162" t="b">
         <v>0</v>
       </c>
       <c r="D162" t="n">
-        <v>0.203633638150063</v>
+        <v>0.6631091691401918</v>
       </c>
       <c r="E162" t="n">
-        <v>0.2468705071649178</v>
+        <v>0.005411051855617241</v>
       </c>
       <c r="F162" t="n">
-        <v>0.5494958546850193</v>
+        <v>0.331479779004191</v>
       </c>
     </row>
     <row r="163">
@@ -4015,13 +4015,13 @@
         <v>1</v>
       </c>
       <c r="D163" t="n">
-        <v>0.5635720586712758</v>
+        <v>0.84213593207301</v>
       </c>
       <c r="E163" t="n">
-        <v>0.08478968199564774</v>
+        <v>0.003636126404369762</v>
       </c>
       <c r="F163" t="n">
-        <v>0.3516382593330765</v>
+        <v>0.1542279415226203</v>
       </c>
     </row>
     <row r="164">
@@ -4037,13 +4037,13 @@
         <v>1</v>
       </c>
       <c r="D164" t="n">
-        <v>0.4976868178243005</v>
+        <v>0.9113983849735523</v>
       </c>
       <c r="E164" t="n">
-        <v>0.05265337502190332</v>
+        <v>0.002276145285916539</v>
       </c>
       <c r="F164" t="n">
-        <v>0.4496598071537961</v>
+        <v>0.08632546974053096</v>
       </c>
     </row>
     <row r="165">
@@ -4059,13 +4059,13 @@
         <v>0</v>
       </c>
       <c r="D165" t="n">
-        <v>0.9572138668814424</v>
+        <v>0.9876164884823414</v>
       </c>
       <c r="E165" t="n">
-        <v>0.003806564327106898</v>
+        <v>0.0114720694223647</v>
       </c>
       <c r="F165" t="n">
-        <v>0.03897956879145081</v>
+        <v>0.0009114420952940469</v>
       </c>
     </row>
     <row r="166">
@@ -4081,13 +4081,13 @@
         <v>1</v>
       </c>
       <c r="D166" t="n">
-        <v>0.6191680064427596</v>
+        <v>0.9175504771243086</v>
       </c>
       <c r="E166" t="n">
-        <v>0.06848775186278876</v>
+        <v>0.004657150531607253</v>
       </c>
       <c r="F166" t="n">
-        <v>0.3123442416944517</v>
+        <v>0.07779237234408422</v>
       </c>
     </row>
     <row r="167">
@@ -4097,19 +4097,19 @@
         </is>
       </c>
       <c r="B167" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C167" t="b">
         <v>0</v>
       </c>
       <c r="D167" t="n">
-        <v>0.2950402700717664</v>
+        <v>0.9326490580898501</v>
       </c>
       <c r="E167" t="n">
-        <v>0.08696639135208102</v>
+        <v>0.03070663838634878</v>
       </c>
       <c r="F167" t="n">
-        <v>0.6179933385761526</v>
+        <v>0.03664430352380127</v>
       </c>
     </row>
     <row r="168">
@@ -4119,19 +4119,19 @@
         </is>
       </c>
       <c r="B168" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C168" t="b">
         <v>0</v>
       </c>
       <c r="D168" t="n">
-        <v>0.3744890920830476</v>
+        <v>0.820566105087423</v>
       </c>
       <c r="E168" t="n">
-        <v>0.03180522289197991</v>
+        <v>0.0002191840598582985</v>
       </c>
       <c r="F168" t="n">
-        <v>0.5937056850249726</v>
+        <v>0.1792147108527187</v>
       </c>
     </row>
     <row r="169">
@@ -4147,13 +4147,13 @@
         <v>1</v>
       </c>
       <c r="D169" t="n">
-        <v>0.8065670218624079</v>
+        <v>0.9827048797501874</v>
       </c>
       <c r="E169" t="n">
-        <v>0.01469817121251673</v>
+        <v>0.002464729253615571</v>
       </c>
       <c r="F169" t="n">
-        <v>0.1787348069250754</v>
+        <v>0.01483039099619709</v>
       </c>
     </row>
     <row r="170">
@@ -4169,13 +4169,13 @@
         <v>1</v>
       </c>
       <c r="D170" t="n">
-        <v>0.5318152132359665</v>
+        <v>0.7371473913958311</v>
       </c>
       <c r="E170" t="n">
-        <v>0.02167967416021431</v>
+        <v>4.382006134879314e-05</v>
       </c>
       <c r="F170" t="n">
-        <v>0.4465051126038194</v>
+        <v>0.2628087885428201</v>
       </c>
     </row>
     <row r="171">
@@ -4185,19 +4185,19 @@
         </is>
       </c>
       <c r="B171" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C171" t="b">
         <v>0</v>
       </c>
       <c r="D171" t="n">
-        <v>0.3242651385356434</v>
+        <v>0.750217247285536</v>
       </c>
       <c r="E171" t="n">
-        <v>0.207354269789892</v>
+        <v>0.01227616345986265</v>
       </c>
       <c r="F171" t="n">
-        <v>0.4683805916744644</v>
+        <v>0.2375065892546014</v>
       </c>
     </row>
     <row r="172">
@@ -4207,19 +4207,19 @@
         </is>
       </c>
       <c r="B172" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C172" t="b">
         <v>1</v>
       </c>
       <c r="D172" t="n">
-        <v>0.4614301897899071</v>
+        <v>0.7727472139541769</v>
       </c>
       <c r="E172" t="n">
-        <v>0.05455567400177713</v>
+        <v>0.0005899545448246134</v>
       </c>
       <c r="F172" t="n">
-        <v>0.4840141362083158</v>
+        <v>0.2266628315009987</v>
       </c>
     </row>
     <row r="173">
@@ -4235,13 +4235,13 @@
         <v>1</v>
       </c>
       <c r="D173" t="n">
-        <v>0.5069250079966386</v>
+        <v>0.7958327839643894</v>
       </c>
       <c r="E173" t="n">
-        <v>0.06197761554245805</v>
+        <v>0.000974049066607456</v>
       </c>
       <c r="F173" t="n">
-        <v>0.4310973764609033</v>
+        <v>0.2031931669690031</v>
       </c>
     </row>
     <row r="174">
@@ -4257,13 +4257,13 @@
         <v>1</v>
       </c>
       <c r="D174" t="n">
-        <v>0.580089823535113</v>
+        <v>0.7748885524660708</v>
       </c>
       <c r="E174" t="n">
-        <v>0.06272480178297511</v>
+        <v>0.000849144307862603</v>
       </c>
       <c r="F174" t="n">
-        <v>0.3571853746819119</v>
+        <v>0.2242623032260667</v>
       </c>
     </row>
     <row r="175">
@@ -4279,13 +4279,13 @@
         <v>1</v>
       </c>
       <c r="D175" t="n">
-        <v>0.4667563513825961</v>
+        <v>0.7209558815693512</v>
       </c>
       <c r="E175" t="n">
-        <v>0.08729703010374729</v>
+        <v>0.0008894939034777275</v>
       </c>
       <c r="F175" t="n">
-        <v>0.4459466185136566</v>
+        <v>0.2781546245271711</v>
       </c>
     </row>
     <row r="176">
@@ -4295,19 +4295,19 @@
         </is>
       </c>
       <c r="B176" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C176" t="b">
         <v>0</v>
       </c>
       <c r="D176" t="n">
-        <v>0.2301862110638882</v>
+        <v>0.7545070890430152</v>
       </c>
       <c r="E176" t="n">
-        <v>0.3295391024474066</v>
+        <v>0.05485606672031924</v>
       </c>
       <c r="F176" t="n">
-        <v>0.4402746864887053</v>
+        <v>0.1906368442366655</v>
       </c>
     </row>
     <row r="177">
@@ -4317,19 +4317,19 @@
         </is>
       </c>
       <c r="B177" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C177" t="b">
         <v>0</v>
       </c>
       <c r="D177" t="n">
-        <v>0.0904645113958476</v>
+        <v>0.6322461879316454</v>
       </c>
       <c r="E177" t="n">
-        <v>0.5307609117787006</v>
+        <v>0.1272595243586125</v>
       </c>
       <c r="F177" t="n">
-        <v>0.3787745768254518</v>
+        <v>0.240494287709742</v>
       </c>
     </row>
     <row r="178">
@@ -4339,19 +4339,19 @@
         </is>
       </c>
       <c r="B178" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C178" t="b">
         <v>0</v>
       </c>
       <c r="D178" t="n">
-        <v>0.05928820032606496</v>
+        <v>0.4923486937312459</v>
       </c>
       <c r="E178" t="n">
-        <v>0.6972297808360004</v>
+        <v>0.2366460275737612</v>
       </c>
       <c r="F178" t="n">
-        <v>0.2434820188379346</v>
+        <v>0.2710052786949929</v>
       </c>
     </row>
     <row r="179">
@@ -4361,19 +4361,19 @@
         </is>
       </c>
       <c r="B179" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C179" t="b">
         <v>0</v>
       </c>
       <c r="D179" t="n">
-        <v>0.2829972063000191</v>
+        <v>0.904181687501399</v>
       </c>
       <c r="E179" t="n">
-        <v>0.03441753301652749</v>
+        <v>0.001038718065024848</v>
       </c>
       <c r="F179" t="n">
-        <v>0.6825852606834535</v>
+        <v>0.09477959443357614</v>
       </c>
     </row>
     <row r="180">
@@ -4383,19 +4383,19 @@
         </is>
       </c>
       <c r="B180" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C180" t="b">
         <v>0</v>
       </c>
       <c r="D180" t="n">
-        <v>0.4070415447186903</v>
+        <v>0.8699232909220019</v>
       </c>
       <c r="E180" t="n">
-        <v>0.04331738648003643</v>
+        <v>0.0007537284765213853</v>
       </c>
       <c r="F180" t="n">
-        <v>0.5496410688012734</v>
+        <v>0.1293229806014766</v>
       </c>
     </row>
     <row r="181">
@@ -4411,13 +4411,13 @@
         <v>0</v>
       </c>
       <c r="D181" t="n">
-        <v>0.02100340587490298</v>
+        <v>0.2320666142093248</v>
       </c>
       <c r="E181" t="n">
-        <v>0.7871006786893854</v>
+        <v>0.6374370241271083</v>
       </c>
       <c r="F181" t="n">
-        <v>0.1918959154357117</v>
+        <v>0.1304963616635668</v>
       </c>
     </row>
     <row r="182">
@@ -4427,19 +4427,19 @@
         </is>
       </c>
       <c r="B182" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C182" t="b">
         <v>0</v>
       </c>
       <c r="D182" t="n">
-        <v>0.2799895984941716</v>
+        <v>0.8639156223169223</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1004226471356702</v>
+        <v>0.00460639875430925</v>
       </c>
       <c r="F182" t="n">
-        <v>0.6195877543701582</v>
+        <v>0.1314779789287684</v>
       </c>
     </row>
     <row r="183">
@@ -4449,19 +4449,19 @@
         </is>
       </c>
       <c r="B183" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C183" t="b">
         <v>0</v>
       </c>
       <c r="D183" t="n">
-        <v>0.299908988125354</v>
+        <v>0.8308855152311898</v>
       </c>
       <c r="E183" t="n">
-        <v>0.02444723926738608</v>
+        <v>0.0002196048868928343</v>
       </c>
       <c r="F183" t="n">
-        <v>0.6756437726072598</v>
+        <v>0.1688948798819173</v>
       </c>
     </row>
     <row r="184">
@@ -4471,19 +4471,19 @@
         </is>
       </c>
       <c r="B184" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C184" t="b">
         <v>0</v>
       </c>
       <c r="D184" t="n">
-        <v>0.1741742820810141</v>
+        <v>0.7388290994466105</v>
       </c>
       <c r="E184" t="n">
-        <v>0.2617667415315099</v>
+        <v>0.01583033586185941</v>
       </c>
       <c r="F184" t="n">
-        <v>0.5640589763874759</v>
+        <v>0.2453405646915301</v>
       </c>
     </row>
     <row r="185">
@@ -4493,19 +4493,19 @@
         </is>
       </c>
       <c r="B185" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C185" t="b">
         <v>0</v>
       </c>
       <c r="D185" t="n">
-        <v>0.1713140207220574</v>
+        <v>0.6903066275160611</v>
       </c>
       <c r="E185" t="n">
-        <v>0.3824575147396191</v>
+        <v>0.04684276588863653</v>
       </c>
       <c r="F185" t="n">
-        <v>0.4462284645383235</v>
+        <v>0.2628506065953023</v>
       </c>
     </row>
     <row r="186">
@@ -4515,19 +4515,19 @@
         </is>
       </c>
       <c r="B186" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C186" t="b">
         <v>0</v>
       </c>
       <c r="D186" t="n">
-        <v>0.1239427797354583</v>
+        <v>0.7498276365040948</v>
       </c>
       <c r="E186" t="n">
-        <v>0.3205360908959294</v>
+        <v>0.04060092271119967</v>
       </c>
       <c r="F186" t="n">
-        <v>0.5555211293686123</v>
+        <v>0.2095714407847055</v>
       </c>
     </row>
     <row r="187">
@@ -4543,13 +4543,13 @@
         <v>0</v>
       </c>
       <c r="D187" t="n">
-        <v>0.5038705070895382</v>
+        <v>0.9287218411556941</v>
       </c>
       <c r="E187" t="n">
-        <v>0.02792097974354401</v>
+        <v>0.000684601159709428</v>
       </c>
       <c r="F187" t="n">
-        <v>0.4682085131669178</v>
+        <v>0.07059355768459641</v>
       </c>
     </row>
     <row r="188">
@@ -4559,19 +4559,19 @@
         </is>
       </c>
       <c r="B188" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C188" t="b">
         <v>1</v>
       </c>
       <c r="D188" t="n">
-        <v>0.3521010194507085</v>
+        <v>0.8129240107516708</v>
       </c>
       <c r="E188" t="n">
-        <v>0.08637729687605138</v>
+        <v>0.002410800069952336</v>
       </c>
       <c r="F188" t="n">
-        <v>0.5615216836732401</v>
+        <v>0.1846651891783768</v>
       </c>
     </row>
     <row r="189">
@@ -4587,13 +4587,13 @@
         <v>1</v>
       </c>
       <c r="D189" t="n">
-        <v>0.6022464835372026</v>
+        <v>0.7903801033358235</v>
       </c>
       <c r="E189" t="n">
-        <v>0.05622028480049232</v>
+        <v>0.0007908391855481508</v>
       </c>
       <c r="F189" t="n">
-        <v>0.3415332316623052</v>
+        <v>0.2088290574786284</v>
       </c>
     </row>
     <row r="190">
@@ -4603,19 +4603,19 @@
         </is>
       </c>
       <c r="B190" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C190" t="b">
         <v>1</v>
       </c>
       <c r="D190" t="n">
-        <v>0.2879463294962945</v>
+        <v>0.6801123487241238</v>
       </c>
       <c r="E190" t="n">
-        <v>0.2675079122769882</v>
+        <v>0.01005377423255643</v>
       </c>
       <c r="F190" t="n">
-        <v>0.4445457582267173</v>
+        <v>0.3098338770433197</v>
       </c>
     </row>
     <row r="191">
@@ -4625,19 +4625,19 @@
         </is>
       </c>
       <c r="B191" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C191" t="b">
         <v>1</v>
       </c>
       <c r="D191" t="n">
-        <v>0.4157999450560583</v>
+        <v>0.5082132303277805</v>
       </c>
       <c r="E191" t="n">
-        <v>0.08916697793615393</v>
+        <v>0.0002573350930629661</v>
       </c>
       <c r="F191" t="n">
-        <v>0.4950330770077877</v>
+        <v>0.4915294345791564</v>
       </c>
     </row>
     <row r="192">
@@ -4647,19 +4647,19 @@
         </is>
       </c>
       <c r="B192" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C192" t="b">
         <v>1</v>
       </c>
       <c r="D192" t="n">
-        <v>0.3066771247883693</v>
+        <v>0.6461985272366956</v>
       </c>
       <c r="E192" t="n">
-        <v>0.2433881365836267</v>
+        <v>0.005331938135341549</v>
       </c>
       <c r="F192" t="n">
-        <v>0.449934738628004</v>
+        <v>0.3484695346279628</v>
       </c>
     </row>
     <row r="193">
@@ -4669,19 +4669,19 @@
         </is>
       </c>
       <c r="B193" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C193" t="b">
         <v>0</v>
       </c>
       <c r="D193" t="n">
-        <v>0.2350632233639555</v>
+        <v>0.7273820629804927</v>
       </c>
       <c r="E193" t="n">
-        <v>0.2118206369885753</v>
+        <v>0.00835560517276193</v>
       </c>
       <c r="F193" t="n">
-        <v>0.5531161396474692</v>
+        <v>0.2642623318467454</v>
       </c>
     </row>
     <row r="194">
@@ -4691,19 +4691,19 @@
         </is>
       </c>
       <c r="B194" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C194" t="b">
         <v>0</v>
       </c>
       <c r="D194" t="n">
-        <v>0.2800026423291745</v>
+        <v>0.8404844101432984</v>
       </c>
       <c r="E194" t="n">
-        <v>0.1835171105638319</v>
+        <v>0.01711846659167832</v>
       </c>
       <c r="F194" t="n">
-        <v>0.5364802471069936</v>
+        <v>0.1423971232650231</v>
       </c>
     </row>
     <row r="195">
@@ -4713,19 +4713,19 @@
         </is>
       </c>
       <c r="B195" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C195" t="b">
         <v>0</v>
       </c>
       <c r="D195" t="n">
-        <v>0.2994490942496619</v>
+        <v>0.8686573800807497</v>
       </c>
       <c r="E195" t="n">
-        <v>0.1719367691852949</v>
+        <v>0.0127922987943266</v>
       </c>
       <c r="F195" t="n">
-        <v>0.5286141365650433</v>
+        <v>0.1185503211249237</v>
       </c>
     </row>
     <row r="196">
@@ -4735,19 +4735,19 @@
         </is>
       </c>
       <c r="B196" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C196" t="b">
         <v>0</v>
       </c>
       <c r="D196" t="n">
-        <v>0.1385643685754022</v>
+        <v>0.705466027266647</v>
       </c>
       <c r="E196" t="n">
-        <v>0.4652033014133279</v>
+        <v>0.1377947748916685</v>
       </c>
       <c r="F196" t="n">
-        <v>0.39623233001127</v>
+        <v>0.1567391978416845</v>
       </c>
     </row>
     <row r="197">
@@ -4757,19 +4757,19 @@
         </is>
       </c>
       <c r="B197" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C197" t="b">
         <v>0</v>
       </c>
       <c r="D197" t="n">
-        <v>0.1135858845124032</v>
+        <v>0.6109840709052146</v>
       </c>
       <c r="E197" t="n">
-        <v>0.4031776442888488</v>
+        <v>0.02127484218519995</v>
       </c>
       <c r="F197" t="n">
-        <v>0.4832364711987481</v>
+        <v>0.3677410869095855</v>
       </c>
     </row>
     <row r="198">
@@ -4779,19 +4779,19 @@
         </is>
       </c>
       <c r="B198" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C198" t="b">
         <v>0</v>
       </c>
       <c r="D198" t="n">
-        <v>0.3209683132977374</v>
+        <v>0.785698099109234</v>
       </c>
       <c r="E198" t="n">
-        <v>0.1409490904075091</v>
+        <v>0.002842383300330105</v>
       </c>
       <c r="F198" t="n">
-        <v>0.5380825962947535</v>
+        <v>0.2114595175904359</v>
       </c>
     </row>
     <row r="199">
@@ -4801,19 +4801,19 @@
         </is>
       </c>
       <c r="B199" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C199" t="b">
         <v>0</v>
       </c>
       <c r="D199" t="n">
-        <v>0.249316240817862</v>
+        <v>0.8009425758350284</v>
       </c>
       <c r="E199" t="n">
-        <v>0.1812406131425566</v>
+        <v>0.006686272496434595</v>
       </c>
       <c r="F199" t="n">
-        <v>0.5694431460395815</v>
+        <v>0.1923711516685369</v>
       </c>
     </row>
     <row r="200">
@@ -4823,19 +4823,19 @@
         </is>
       </c>
       <c r="B200" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C200" t="b">
         <v>0</v>
       </c>
       <c r="D200" t="n">
-        <v>0.153218555089094</v>
+        <v>0.7737199886911269</v>
       </c>
       <c r="E200" t="n">
-        <v>0.3005421359221543</v>
+        <v>0.03929267490481881</v>
       </c>
       <c r="F200" t="n">
-        <v>0.5462393089887517</v>
+        <v>0.1869873364040544</v>
       </c>
     </row>
     <row r="201">
@@ -4845,19 +4845,19 @@
         </is>
       </c>
       <c r="B201" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C201" t="b">
         <v>0</v>
       </c>
       <c r="D201" t="n">
-        <v>0.1381940082155443</v>
+        <v>0.6858096193489438</v>
       </c>
       <c r="E201" t="n">
-        <v>0.41711242338964</v>
+        <v>0.1001620723149506</v>
       </c>
       <c r="F201" t="n">
-        <v>0.4446935683948158</v>
+        <v>0.2140283083361055</v>
       </c>
     </row>
     <row r="202">
@@ -4873,13 +4873,13 @@
         <v>0</v>
       </c>
       <c r="D202" t="n">
-        <v>0.09145951922247991</v>
+        <v>0.2621704154243427</v>
       </c>
       <c r="E202" t="n">
-        <v>0.6386853357521781</v>
+        <v>0.6664898845584732</v>
       </c>
       <c r="F202" t="n">
-        <v>0.2698551450253419</v>
+        <v>0.07133970001718412</v>
       </c>
     </row>
     <row r="203">
@@ -4895,13 +4895,13 @@
         <v>1</v>
       </c>
       <c r="D203" t="n">
-        <v>0.555668141646107</v>
+        <v>0.7799293646860298</v>
       </c>
       <c r="E203" t="n">
-        <v>0.06885540293886691</v>
+        <v>0.0009935597457388474</v>
       </c>
       <c r="F203" t="n">
-        <v>0.3754764554150261</v>
+        <v>0.2190770755682313</v>
       </c>
     </row>
     <row r="204">
@@ -4911,19 +4911,19 @@
         </is>
       </c>
       <c r="B204" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C204" t="b">
         <v>0</v>
       </c>
       <c r="D204" t="n">
-        <v>0.2228661705703458</v>
+        <v>0.7065581064763897</v>
       </c>
       <c r="E204" t="n">
-        <v>0.1231855248432867</v>
+        <v>0.003263075920976113</v>
       </c>
       <c r="F204" t="n">
-        <v>0.6539483045863677</v>
+        <v>0.2901788176026342</v>
       </c>
     </row>
     <row r="205">
@@ -4933,19 +4933,19 @@
         </is>
       </c>
       <c r="B205" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C205" t="b">
         <v>0</v>
       </c>
       <c r="D205" t="n">
-        <v>0.3403128379565661</v>
+        <v>0.8020301347594798</v>
       </c>
       <c r="E205" t="n">
-        <v>0.1063005931513471</v>
+        <v>0.002315733504688593</v>
       </c>
       <c r="F205" t="n">
-        <v>0.5533865688920868</v>
+        <v>0.1956541317358315</v>
       </c>
     </row>
     <row r="206">
@@ -4955,19 +4955,19 @@
         </is>
       </c>
       <c r="B206" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C206" t="b">
         <v>0</v>
       </c>
       <c r="D206" t="n">
-        <v>0.3420451445418619</v>
+        <v>0.6962766665748021</v>
       </c>
       <c r="E206" t="n">
-        <v>0.1097489685018393</v>
+        <v>0.001209610768170636</v>
       </c>
       <c r="F206" t="n">
-        <v>0.5482058869562989</v>
+        <v>0.3025137226570273</v>
       </c>
     </row>
     <row r="207">
@@ -4977,19 +4977,19 @@
         </is>
       </c>
       <c r="B207" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C207" t="b">
         <v>1</v>
       </c>
       <c r="D207" t="n">
-        <v>0.2813059165474168</v>
+        <v>0.5447148810150164</v>
       </c>
       <c r="E207" t="n">
-        <v>0.06864335198980148</v>
+        <v>0.000255215868638442</v>
       </c>
       <c r="F207" t="n">
-        <v>0.6500507314627816</v>
+        <v>0.4550299031163452</v>
       </c>
     </row>
     <row r="208">
@@ -4999,19 +4999,19 @@
         </is>
       </c>
       <c r="B208" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C208" t="b">
         <v>1</v>
       </c>
       <c r="D208" t="n">
-        <v>0.2136247707255321</v>
+        <v>0.639378787935898</v>
       </c>
       <c r="E208" t="n">
-        <v>0.3822784591009425</v>
+        <v>0.02982768684107812</v>
       </c>
       <c r="F208" t="n">
-        <v>0.4040967701735254</v>
+        <v>0.330793525223024</v>
       </c>
     </row>
     <row r="209">
@@ -5021,19 +5021,19 @@
         </is>
       </c>
       <c r="B209" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C209" t="b">
         <v>1</v>
       </c>
       <c r="D209" t="n">
-        <v>0.1812931000986273</v>
+        <v>0.5138938348130593</v>
       </c>
       <c r="E209" t="n">
-        <v>0.3148495772612373</v>
+        <v>0.01039917345797956</v>
       </c>
       <c r="F209" t="n">
-        <v>0.5038573226401355</v>
+        <v>0.4757069917289611</v>
       </c>
     </row>
     <row r="210">
@@ -5043,19 +5043,19 @@
         </is>
       </c>
       <c r="B210" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C210" t="b">
         <v>1</v>
       </c>
       <c r="D210" t="n">
-        <v>0.2562442585369242</v>
+        <v>0.7527699022283815</v>
       </c>
       <c r="E210" t="n">
-        <v>0.239365821992594</v>
+        <v>0.01252478408421505</v>
       </c>
       <c r="F210" t="n">
-        <v>0.5043899194704818</v>
+        <v>0.2347053136874033</v>
       </c>
     </row>
     <row r="211">
@@ -5065,19 +5065,19 @@
         </is>
       </c>
       <c r="B211" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C211" t="b">
         <v>0</v>
       </c>
       <c r="D211" t="n">
-        <v>0.3252321501881797</v>
+        <v>0.9093770883902393</v>
       </c>
       <c r="E211" t="n">
-        <v>0.1377938249035272</v>
+        <v>0.01642832555908301</v>
       </c>
       <c r="F211" t="n">
-        <v>0.536974024908293</v>
+        <v>0.07419458605067748</v>
       </c>
     </row>
     <row r="212">
@@ -5087,19 +5087,19 @@
         </is>
       </c>
       <c r="B212" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C212" t="b">
         <v>1</v>
       </c>
       <c r="D212" t="n">
-        <v>0.3810865897534437</v>
+        <v>0.8423713775849021</v>
       </c>
       <c r="E212" t="n">
-        <v>0.2194553777079356</v>
+        <v>0.02785063814372586</v>
       </c>
       <c r="F212" t="n">
-        <v>0.3994580325386208</v>
+        <v>0.129777984271372</v>
       </c>
     </row>
     <row r="213">
@@ -5115,13 +5115,13 @@
         <v>1</v>
       </c>
       <c r="D213" t="n">
-        <v>0.4731655810720934</v>
+        <v>0.8083010097910375</v>
       </c>
       <c r="E213" t="n">
-        <v>0.1056497942504016</v>
+        <v>0.002936220330340001</v>
       </c>
       <c r="F213" t="n">
-        <v>0.4211846246775051</v>
+        <v>0.1887627698786225</v>
       </c>
     </row>
     <row r="214">
@@ -5131,19 +5131,19 @@
         </is>
       </c>
       <c r="B214" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C214" t="b">
         <v>0</v>
       </c>
       <c r="D214" t="n">
-        <v>0.2513737062427884</v>
+        <v>0.7710547175664713</v>
       </c>
       <c r="E214" t="n">
-        <v>0.311237905408197</v>
+        <v>0.1785508200109912</v>
       </c>
       <c r="F214" t="n">
-        <v>0.4373883883490146</v>
+        <v>0.05039446242253749</v>
       </c>
     </row>
     <row r="215">
@@ -5159,13 +5159,13 @@
         <v>1</v>
       </c>
       <c r="D215" t="n">
-        <v>0.4253764540101057</v>
+        <v>0.7145253893522687</v>
       </c>
       <c r="E215" t="n">
-        <v>0.2876849964446676</v>
+        <v>0.2191941810731493</v>
       </c>
       <c r="F215" t="n">
-        <v>0.2869385495452268</v>
+        <v>0.06628042957458186</v>
       </c>
     </row>
     <row r="216">
@@ -5181,13 +5181,13 @@
         <v>0</v>
       </c>
       <c r="D216" t="n">
-        <v>0.5457605109898185</v>
+        <v>0.9040331953580522</v>
       </c>
       <c r="E216" t="n">
-        <v>0.1147177493832636</v>
+        <v>0.01455361512653315</v>
       </c>
       <c r="F216" t="n">
-        <v>0.339521739626918</v>
+        <v>0.08141318951541475</v>
       </c>
     </row>
     <row r="217">
@@ -5203,13 +5203,13 @@
         <v>0</v>
       </c>
       <c r="D217" t="n">
-        <v>0.003652689730292071</v>
+        <v>0.0003359696238841376</v>
       </c>
       <c r="E217" t="n">
-        <v>0.9716977835097051</v>
+        <v>0.9996267008908861</v>
       </c>
       <c r="F217" t="n">
-        <v>0.02464952676000293</v>
+        <v>3.732948522979166e-05</v>
       </c>
     </row>
     <row r="218">
@@ -5219,19 +5219,19 @@
         </is>
       </c>
       <c r="B218" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C218" t="b">
         <v>0</v>
       </c>
       <c r="D218" t="n">
-        <v>0.241630776066862</v>
+        <v>0.9415588573606873</v>
       </c>
       <c r="E218" t="n">
-        <v>0.03986245324476446</v>
+        <v>0.04904813259733888</v>
       </c>
       <c r="F218" t="n">
-        <v>0.7185067706883735</v>
+        <v>0.009393010041973758</v>
       </c>
     </row>
     <row r="219">
@@ -5241,19 +5241,19 @@
         </is>
       </c>
       <c r="B219" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C219" t="b">
         <v>0</v>
       </c>
       <c r="D219" t="n">
-        <v>0.2330386465571614</v>
+        <v>0.8791088381754214</v>
       </c>
       <c r="E219" t="n">
-        <v>0.1668812587629836</v>
+        <v>0.08109190486296775</v>
       </c>
       <c r="F219" t="n">
-        <v>0.600080094679855</v>
+        <v>0.03979925696161093</v>
       </c>
     </row>
     <row r="220">
@@ -5269,13 +5269,13 @@
         <v>0</v>
       </c>
       <c r="D220" t="n">
-        <v>0.008342614491398798</v>
+        <v>0.0009985728772357713</v>
       </c>
       <c r="E220" t="n">
-        <v>0.9315581073603396</v>
+        <v>0.9989428041174885</v>
       </c>
       <c r="F220" t="n">
-        <v>0.06009927814826152</v>
+        <v>5.862300527558505e-05</v>
       </c>
     </row>
     <row r="221">
@@ -5285,19 +5285,19 @@
         </is>
       </c>
       <c r="B221" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C221" t="b">
         <v>0</v>
       </c>
       <c r="D221" t="n">
-        <v>0.1041338251791805</v>
+        <v>0.6463753292761589</v>
       </c>
       <c r="E221" t="n">
-        <v>0.3398367475205679</v>
+        <v>0.3134390111649097</v>
       </c>
       <c r="F221" t="n">
-        <v>0.5560294273002517</v>
+        <v>0.04018565955893139</v>
       </c>
     </row>
     <row r="222">
@@ -5307,19 +5307,19 @@
         </is>
       </c>
       <c r="B222" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C222" t="b">
         <v>0</v>
       </c>
       <c r="D222" t="n">
-        <v>0.2417577499460689</v>
+        <v>0.7240352337591339</v>
       </c>
       <c r="E222" t="n">
-        <v>0.3713947711505168</v>
+        <v>0.03773271656700446</v>
       </c>
       <c r="F222" t="n">
-        <v>0.3868474789034143</v>
+        <v>0.2382320496738616</v>
       </c>
     </row>
     <row r="223">
@@ -5335,13 +5335,13 @@
         <v>0</v>
       </c>
       <c r="D223" t="n">
-        <v>0.02037183788991435</v>
+        <v>0.007919633323500999</v>
       </c>
       <c r="E223" t="n">
-        <v>0.8974150360103273</v>
+        <v>0.9911519891160319</v>
       </c>
       <c r="F223" t="n">
-        <v>0.08221312609975835</v>
+        <v>0.0009283775604670263</v>
       </c>
     </row>
     <row r="224">
@@ -5351,19 +5351,19 @@
         </is>
       </c>
       <c r="B224" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C224" t="b">
         <v>0</v>
       </c>
       <c r="D224" t="n">
-        <v>0.3634129308768106</v>
+        <v>0.92560059936701</v>
       </c>
       <c r="E224" t="n">
-        <v>0.08769136723138511</v>
+        <v>0.03431048794664263</v>
       </c>
       <c r="F224" t="n">
-        <v>0.5488957018918043</v>
+        <v>0.04008891268634743</v>
       </c>
     </row>
     <row r="225">
@@ -5373,19 +5373,19 @@
         </is>
       </c>
       <c r="B225" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C225" t="b">
         <v>0</v>
       </c>
       <c r="D225" t="n">
-        <v>0.2868296610503703</v>
+        <v>0.9646623164052708</v>
       </c>
       <c r="E225" t="n">
-        <v>0.03559215907513591</v>
+        <v>0.007843194131419182</v>
       </c>
       <c r="F225" t="n">
-        <v>0.6775781798744938</v>
+        <v>0.02749448946331012</v>
       </c>
     </row>
     <row r="226">
@@ -5401,13 +5401,13 @@
         <v>0</v>
       </c>
       <c r="D226" t="n">
-        <v>0.06863017083137497</v>
+        <v>0.06951029072023149</v>
       </c>
       <c r="E226" t="n">
-        <v>0.7875915605396079</v>
+        <v>0.9265541602208073</v>
       </c>
       <c r="F226" t="n">
-        <v>0.1437782686290172</v>
+        <v>0.00393554905896124</v>
       </c>
     </row>
     <row r="227">
@@ -5423,13 +5423,13 @@
         <v>0</v>
       </c>
       <c r="D227" t="n">
-        <v>0.5193399869300935</v>
+        <v>0.7069390178550464</v>
       </c>
       <c r="E227" t="n">
-        <v>0.07701740438980806</v>
+        <v>0.0007916569776432192</v>
       </c>
       <c r="F227" t="n">
-        <v>0.4036426086800984</v>
+        <v>0.2922693251673103</v>
       </c>
     </row>
     <row r="228">
@@ -5445,13 +5445,13 @@
         <v>0</v>
       </c>
       <c r="D228" t="n">
-        <v>0.5870789881227949</v>
+        <v>0.8967589435213299</v>
       </c>
       <c r="E228" t="n">
-        <v>0.06079536487144199</v>
+        <v>0.002512830896651625</v>
       </c>
       <c r="F228" t="n">
-        <v>0.3521256470057631</v>
+        <v>0.1007282255820184</v>
       </c>
     </row>
     <row r="229">
@@ -5461,19 +5461,19 @@
         </is>
       </c>
       <c r="B229" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C229" t="b">
         <v>0</v>
       </c>
       <c r="D229" t="n">
-        <v>0.2026034927420593</v>
+        <v>0.9850211981959422</v>
       </c>
       <c r="E229" t="n">
-        <v>0.007786283053776771</v>
+        <v>0.001042602108426046</v>
       </c>
       <c r="F229" t="n">
-        <v>0.789610224204164</v>
+        <v>0.01393619969563162</v>
       </c>
     </row>
     <row r="230">
@@ -5483,19 +5483,19 @@
         </is>
       </c>
       <c r="B230" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C230" t="b">
         <v>0</v>
       </c>
       <c r="D230" t="n">
-        <v>0.2482589449339731</v>
+        <v>0.6270663835002019</v>
       </c>
       <c r="E230" t="n">
-        <v>0.3961804776866818</v>
+        <v>0.1350451696546889</v>
       </c>
       <c r="F230" t="n">
-        <v>0.3555605773793452</v>
+        <v>0.2378884468451093</v>
       </c>
     </row>
     <row r="231">
@@ -5505,19 +5505,19 @@
         </is>
       </c>
       <c r="B231" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C231" t="b">
         <v>0</v>
       </c>
       <c r="D231" t="n">
-        <v>0.294080985387244</v>
+        <v>0.6688218601312674</v>
       </c>
       <c r="E231" t="n">
-        <v>0.02292011659731947</v>
+        <v>4.924017524458794e-05</v>
       </c>
       <c r="F231" t="n">
-        <v>0.6829988980154365</v>
+        <v>0.3311288996934881</v>
       </c>
     </row>
     <row r="232">
@@ -5527,19 +5527,19 @@
         </is>
       </c>
       <c r="B232" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C232" t="b">
         <v>0</v>
       </c>
       <c r="D232" t="n">
-        <v>0.3226517018333666</v>
+        <v>0.7537572859932392</v>
       </c>
       <c r="E232" t="n">
-        <v>0.01968025913443146</v>
+        <v>5.879578944187089e-05</v>
       </c>
       <c r="F232" t="n">
-        <v>0.6576680390322021</v>
+        <v>0.2461839182173191</v>
       </c>
     </row>
     <row r="233">
@@ -5549,19 +5549,19 @@
         </is>
       </c>
       <c r="B233" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C233" t="b">
         <v>0</v>
       </c>
       <c r="D233" t="n">
-        <v>0.2374843288799317</v>
+        <v>0.7477112851042271</v>
       </c>
       <c r="E233" t="n">
-        <v>0.1596184103836873</v>
+        <v>0.004471149844186176</v>
       </c>
       <c r="F233" t="n">
-        <v>0.6028972607363811</v>
+        <v>0.2478175650515869</v>
       </c>
     </row>
     <row r="234">
@@ -5571,19 +5571,19 @@
         </is>
       </c>
       <c r="B234" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C234" t="b">
         <v>0</v>
       </c>
       <c r="D234" t="n">
-        <v>0.3831777989406981</v>
+        <v>0.8500166447527607</v>
       </c>
       <c r="E234" t="n">
-        <v>0.01103369969389099</v>
+        <v>2.753793778449532e-05</v>
       </c>
       <c r="F234" t="n">
-        <v>0.6057885013654108</v>
+        <v>0.1499558173094546</v>
       </c>
     </row>
   </sheetData>
